--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -546,7 +546,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Sanjeev Giri</t>
+          <t>Sabin Giri</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -564,14 +564,14 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -582,36 +582,54 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Sunil Chaudhary</t>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B7" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="C6" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>66.7%</t>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -670,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>87.5%</t>
         </is>
       </c>
     </row>
@@ -697,15 +715,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -721,20 +740,25 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -753,13 +777,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="6" t="n">
-        <v>5</v>
+      <c r="F2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -778,9 +805,12 @@
         <v>0</v>
       </c>
       <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="G3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -797,13 +827,16 @@
         <v>1</v>
       </c>
       <c r="D4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="F4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F4" s="4" t="n">
-        <v>6</v>
+      <c r="G4" s="4" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -817,7 +850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX7"/>
+  <dimension ref="A1:AX9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -846,12 +879,12 @@
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="25" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="24" customWidth="1" min="32" max="32"/>
+    <col width="27" customWidth="1" min="32" max="32"/>
     <col width="26" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -1299,10 +1332,8 @@
           <t>Som lal gurung</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9869167295</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9869167295</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1388,10 +1419,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
@@ -1402,7 +1431,7 @@
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">
@@ -1503,10 +1532,8 @@
           <t>Sarswati Poudel</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9869886323</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9869886323</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1541,10 +1568,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>27.6726</t>
-        </is>
+      <c r="Y4" s="3" t="n">
+        <v>27.6726</v>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
@@ -1600,25 +1625,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>2,15</t>
         </is>
       </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>85.35099</t>
-        </is>
+      <c r="AP4" s="3" t="n">
+        <v>85.35099</v>
       </c>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
@@ -1719,10 +1740,8 @@
           <t>Bina Kc</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9842653891</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9842653891</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1757,10 +1776,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>27.726284</t>
-        </is>
+      <c r="Y5" s="3" t="n">
+        <v>27.726284</v>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
@@ -1816,25 +1833,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>L19-4</t>
         </is>
       </c>
-      <c r="AP5" s="3" t="inlineStr">
-        <is>
-          <t>85.333615</t>
-        </is>
+      <c r="AP5" s="3" t="n">
+        <v>85.33361499999999</v>
       </c>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">
@@ -1935,10 +1948,8 @@
           <t>Rasid rimal</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9840000161</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9840000161</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -2024,10 +2035,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
@@ -2038,7 +2047,7 @@
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">
@@ -2139,10 +2148,8 @@
           <t>Ashrine Banu</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9741699347</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9741699347</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -2232,10 +2239,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
@@ -2246,37 +2251,469 @@
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>14h 9m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS7" s="3" t="inlineStr">
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX7" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 10:54 AM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351778</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Bijan Shakya</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Bijan Shakya</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9841248747</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 10:54:20 AM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>9841248747</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 05:28:03 PM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 10:54:20 AM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>27.70499</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>Near Pashupati Vision Complex, Pinglasthan, Pashupatinath Marg, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr"/>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>03:26 hour</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>L43-4</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>85.3461</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT7" s="3" t="inlineStr">
-        <is>
-          <t>14h 9m</t>
-        </is>
-      </c>
-      <c r="AU7" s="3" t="inlineStr">
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>17h 26m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV7" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="AW7" s="3" t="inlineStr">
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX7" s="3" t="inlineStr">
-        <is>
-          <t>Rajesh Maharjan</t>
+      <c r="AX8" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 10:57 AM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351207</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Rama Shrestha</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Rama Shrestha</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9861473532</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 10:57:01 AM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>9861473532</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:22:28 AM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 10:57:01 AM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t>27.728</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu,Thamel,Sarkaridhara,Near Nabodit College, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>shrestharama65@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>09:35 hour</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>L21-2</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr">
+        <is>
+          <t>85.31464</t>
+        </is>
+      </c>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>23h 34m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX9" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -528,50 +528,50 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Rajesh Maharjan</t>
+          <t>Ajit Shrestha</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Sabin Giri</t>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Sanjeev Giri</t>
+          <t>Sabin Giri</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -582,14 +582,14 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
@@ -600,36 +600,54 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Sunil Chaudhary</t>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B8" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C8" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="C7" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>75.0%</t>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -688,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>90.0%</t>
         </is>
       </c>
     </row>
@@ -715,16 +733,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -735,30 +754,35 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -771,22 +795,25 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G2" s="6" t="n">
-        <v>7</v>
+      <c r="G2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" s="6" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -808,9 +835,12 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="H3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -821,22 +851,25 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="D4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="E4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="F4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="G4" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -850,7 +883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX9"/>
+  <dimension ref="A1:AX11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -863,10 +896,10 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="32" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="32" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="25" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -884,7 +917,7 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="27" customWidth="1" min="32" max="32"/>
+    <col width="31" customWidth="1" min="32" max="32"/>
     <col width="26" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -2352,10 +2385,8 @@
           <t>Bijan Shakya</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9841248747</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9841248747</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2390,10 +2421,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>27.70499</t>
-        </is>
+      <c r="Y8" s="3" t="n">
+        <v>27.70499</v>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
@@ -2445,25 +2474,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>L43-4</t>
         </is>
       </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>85.3461</t>
-        </is>
+      <c r="AP8" s="3" t="n">
+        <v>85.34610000000001</v>
       </c>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
@@ -2564,10 +2589,8 @@
           <t>Rama Shrestha</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9861473532</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9861473532</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2602,10 +2625,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>27.728</t>
-        </is>
+      <c r="Y9" s="3" t="n">
+        <v>27.728</v>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
@@ -2643,10 +2664,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH9" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH9" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI9" s="3" t="inlineStr">
         <is>
@@ -2665,55 +2684,483 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
           <t>L21-2</t>
         </is>
       </c>
-      <c r="AP9" s="3" t="inlineStr">
-        <is>
-          <t>85.31464</t>
-        </is>
+      <c r="AP9" s="3" t="n">
+        <v>85.31464</v>
       </c>
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>23h 34m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS9" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT9" s="3" t="inlineStr">
-        <is>
-          <t>23h 34m</t>
-        </is>
-      </c>
-      <c r="AU9" s="3" t="inlineStr">
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX9" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 11:15 AM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>WIFI6 Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351280</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Ramjanaki Hydropower Pvt.Ltd.</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Ramjanaki Hydropower Pvt.Ltd.</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9762414088</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:00:28 PM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>mizu_fttx</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:00:14 PM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 11:15:53 AM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>27.694534</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>Ramesh Complex, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>manoj.pradhan@rameshcorp.com</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr">
+        <is>
+          <t>09:15 hour</t>
+        </is>
+      </c>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Binod Dhami</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>CDB175</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr">
+        <is>
+          <t>85.311309</t>
+        </is>
+      </c>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>23h 15m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>23h 15m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV9" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW9" s="3" t="inlineStr">
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX9" s="3" t="inlineStr">
-        <is>
-          <t>Sanjeev Giri</t>
+      <c r="AX10" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 11:12 AM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>TKT1349790</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Bebika Tamrakar</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Bebika Tamrakar</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>9841278497</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 12:03:34 PM</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>9841278497</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 12:03:34 PM</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 11:12:33 AM</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>27.68935</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>Near Nepa Futsal &amp; Recreation, Chaumati, Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr">
+        <is>
+          <t>bebika_tamrakar@yahoo.com</t>
+        </is>
+      </c>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr">
+        <is>
+          <t>19:09 hour</t>
+        </is>
+      </c>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>3,3</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr">
+        <is>
+          <t>85.26405</t>
+        </is>
+      </c>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 8m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 8m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX11" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="C8" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="C8" s="4" t="n">
-        <v>8</v>
-      </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>76.9%</t>
         </is>
       </c>
     </row>
@@ -662,10 +662,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
@@ -702,23 +702,46 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>7.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B3" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>88.9%</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>90.0%</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>76.9%</t>
         </is>
       </c>
     </row>
@@ -733,7 +756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -845,31 +868,59 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Payment Inquiry</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" s="4" t="n">
+      <c r="E5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H4" s="4" t="n">
-        <v>10</v>
+      <c r="H5" s="4" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -883,7 +934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX11"/>
+  <dimension ref="A1:AX14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -901,7 +952,7 @@
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="32" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
@@ -911,7 +962,7 @@
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="25" customWidth="1" min="26" max="26"/>
+    <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
@@ -934,7 +985,7 @@
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
-    <col width="20" customWidth="1" min="49" max="49"/>
+    <col width="25" customWidth="1" min="49" max="49"/>
     <col width="23" customWidth="1" min="50" max="50"/>
   </cols>
   <sheetData>
@@ -2799,10 +2850,8 @@
           <t>Ramjanaki Hydropower Pvt.Ltd.</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9762414088</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9762414088</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -2837,10 +2886,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t>27.694534</t>
-        </is>
+      <c r="Y10" s="3" t="n">
+        <v>27.694534</v>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
@@ -2896,25 +2943,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
           <t>CDB175</t>
         </is>
       </c>
-      <c r="AP10" s="3" t="inlineStr">
-        <is>
-          <t>85.311309</t>
-        </is>
+      <c r="AP10" s="3" t="n">
+        <v>85.31130899999999</v>
       </c>
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI6 Router Upgrade  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
@@ -3015,10 +3058,8 @@
           <t>Bebika Tamrakar</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>9841278497</t>
-        </is>
+      <c r="O11" s="3" t="n">
+        <v>9841278497</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
@@ -3053,10 +3094,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>27.68935</t>
-        </is>
+      <c r="Y11" s="3" t="n">
+        <v>27.68935</v>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
@@ -3112,55 +3151,591 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN11" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN11" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
           <t>3,3</t>
         </is>
       </c>
-      <c r="AP11" s="3" t="inlineStr">
-        <is>
-          <t>85.26405</t>
-        </is>
+      <c r="AP11" s="3" t="n">
+        <v>85.26405</v>
       </c>
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 8m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 8m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS11" s="3" t="inlineStr">
-        <is>
-          <t>1d 23h 8m</t>
-        </is>
-      </c>
-      <c r="AT11" s="3" t="inlineStr">
-        <is>
-          <t>1d 23h 8m</t>
-        </is>
-      </c>
-      <c r="AU11" s="3" t="inlineStr">
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX11" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 11:19 AM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>WIFI6 Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351280</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Ramjanaki Hydropower Pvt.Ltd.</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Ramjanaki Hydropower Pvt.Ltd.</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9762414088</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:00:28 PM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>mizu_fttx</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:00:14 PM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 11:19:16 AM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>27.694534</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>Ramesh Complex, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr">
+        <is>
+          <t>manoj.pradhan@rameshcorp.com</t>
+        </is>
+      </c>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>09:15 hour</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Binod Dhami</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>CDB175</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>85.311309</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>23h 18m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>23h 19m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="AV11" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW11" s="3" t="inlineStr">
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX11" s="3" t="inlineStr">
-        <is>
-          <t>Sunil Chaudhary</t>
+      <c r="AX12" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 11:24 AM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr"/>
+      <c r="J13" s="3" t="inlineStr"/>
+      <c r="K13" s="3" t="inlineStr"/>
+      <c r="L13" s="3" t="inlineStr"/>
+      <c r="M13" s="3" t="inlineStr"/>
+      <c r="N13" s="3" t="inlineStr"/>
+      <c r="O13" s="3" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr"/>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr"/>
+      <c r="V13" s="3" t="inlineStr"/>
+      <c r="W13" s="3" t="inlineStr"/>
+      <c r="X13" s="3" t="inlineStr"/>
+      <c r="Y13" s="3" t="inlineStr"/>
+      <c r="Z13" s="3" t="inlineStr"/>
+      <c r="AA13" s="3" t="inlineStr"/>
+      <c r="AB13" s="3" t="inlineStr"/>
+      <c r="AC13" s="3" t="inlineStr"/>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr"/>
+      <c r="AF13" s="3" t="inlineStr"/>
+      <c r="AG13" s="3" t="inlineStr"/>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr"/>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr"/>
+      <c r="AM13" s="3" t="inlineStr"/>
+      <c r="AN13" s="3" t="inlineStr"/>
+      <c r="AO13" s="3" t="inlineStr"/>
+      <c r="AP13" s="3" t="inlineStr"/>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX13" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 11:20 AM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : not connect internet  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>not connect internet</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>TKT1342375</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Yubraj Shrestha</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Yubraj Shrestha</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>9861976388</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>Sales / Billing Related Issue</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 11:20:50 AM</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>KLK9861976388</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 12:44:29 PM</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 11:20:50 AM</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>Sales / Billing Related Issue</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-CG Group</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="AE14" s="3" t="inlineStr">
+        <is>
+          <t>27.7370218833848, 85.30906817374883 GPS Coordinates, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF14" s="3" t="inlineStr">
+        <is>
+          <t>9861976388@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG14" s="3" t="inlineStr">
+        <is>
+          <t>Payment Inquiry</t>
+        </is>
+      </c>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr">
+        <is>
+          <t>20:36 hour</t>
+        </is>
+      </c>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr"/>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>L48-7</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>Case : not connect internet  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>7d 22h 36m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : not connect internet  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX14" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>13.3%</t>
         </is>
       </c>
     </row>
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>9</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>73.3%</t>
         </is>
       </c>
     </row>
@@ -756,10 +756,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -830,19 +830,19 @@
         <v>2</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>2</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -855,13 +855,13 @@
         <v>0</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" s="6" t="n">
         <v>1</v>
@@ -870,7 +870,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Payment Inquiry</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -883,44 +883,72 @@
         <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Payment Inquiry</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E6" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>11</v>
+      <c r="H6" s="4" t="n">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -934,7 +962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX14"/>
+  <dimension ref="A1:AX16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -969,7 +997,7 @@
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
     <col width="31" customWidth="1" min="32" max="32"/>
-    <col width="26" customWidth="1" min="33" max="33"/>
+    <col width="28" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -3266,10 +3294,8 @@
           <t>Ramjanaki Hydropower Pvt.Ltd.</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9762414088</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9762414088</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -3304,10 +3330,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>27.694534</t>
-        </is>
+      <c r="Y12" s="3" t="n">
+        <v>27.694534</v>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
@@ -3363,25 +3387,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>CDB175</t>
         </is>
       </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>85.311309</t>
-        </is>
+      <c r="AP12" s="3" t="n">
+        <v>85.31130899999999</v>
       </c>
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI6 Router Upgrade  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
@@ -3590,10 +3610,8 @@
           <t>Yubraj Shrestha</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>9861976388</t>
-        </is>
+      <c r="O14" s="3" t="n">
+        <v>9861976388</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
@@ -3628,10 +3646,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y14" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
@@ -3687,55 +3703,475 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN14" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
           <t>L48-7</t>
         </is>
       </c>
-      <c r="AP14" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>7d 22h 36m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
           <t>Case : not connect internet  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS14" s="3" t="inlineStr">
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX14" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 11:37 AM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb box issue   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>stb box issue</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352007</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Dilumaya Lamsal</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Dilumaya Lamsal</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>9841677380</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 11:37:19 AM</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>9841677380</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 08:47:30 PM</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 11:37:19 AM</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr">
+        <is>
+          <t>27.74025</t>
+        </is>
+      </c>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA15" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC15" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr">
+        <is>
+          <t>Gongabu , ganesthan, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF15" s="3" t="inlineStr"/>
+      <c r="AG15" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH15" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI15" s="3" t="inlineStr">
+        <is>
+          <t>01:37 hour</t>
+        </is>
+      </c>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr">
+        <is>
+          <t>Keshab Magar</t>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>L58-5</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr">
+        <is>
+          <t>85.31402</t>
+        </is>
+      </c>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb box issue   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT14" s="3" t="inlineStr">
-        <is>
-          <t>7d 22h 36m</t>
-        </is>
-      </c>
-      <c r="AU14" s="3" t="inlineStr">
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>14h 49m</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV14" s="3" t="inlineStr">
-        <is>
-          <t>Case : not connect internet  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW14" s="3" t="inlineStr">
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb box issue   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="AX14" s="3" t="inlineStr">
+      <c r="AX15" s="3" t="inlineStr">
         <is>
           <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 11:40 AM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>TKT1349824</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Shreya Acharya</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Shreya Acharya</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>9852030441</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 11:40:52 AM</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>BKT9802720357</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 12:19:31 PM</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 11:40:52 AM</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr"/>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr">
+        <is>
+          <t>KG MART -Kirana Ghar Suppliers - Department store Suryabinayak 04 Madhyapur Thimi, Bhaktapur, Nepal,</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="inlineStr">
+        <is>
+          <t>Acharyashreya15@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG16" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr">
+        <is>
+          <t>19:21 hour</t>
+        </is>
+      </c>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>1,8</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr"/>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 21m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX16" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>82.4%</t>
         </is>
       </c>
     </row>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>17.6%</t>
         </is>
       </c>
     </row>
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>10</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>70.6%</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>1</v>
@@ -830,13 +830,13 @@
         <v>2</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>2</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -933,7 +933,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>1</v>
@@ -942,13 +942,13 @@
         <v>4</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>3</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -962,7 +962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX16"/>
+  <dimension ref="A1:AX18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -3818,10 +3818,8 @@
           <t>Dilumaya Lamsal</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>9841677380</t>
-        </is>
+      <c r="O15" s="3" t="n">
+        <v>9841677380</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
@@ -3856,10 +3854,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y15" s="3" t="inlineStr">
-        <is>
-          <t>27.74025</t>
-        </is>
+      <c r="Y15" s="3" t="n">
+        <v>27.74025</v>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
@@ -3893,10 +3889,8 @@
           <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
-      <c r="AH15" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH15" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI15" s="3" t="inlineStr">
         <is>
@@ -3915,25 +3909,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN15" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
           <t>L58-5</t>
         </is>
       </c>
-      <c r="AP15" s="3" t="inlineStr">
-        <is>
-          <t>85.31402</t>
-        </is>
+      <c r="AP15" s="3" t="n">
+        <v>85.31402</v>
       </c>
       <c r="AQ15" s="3" t="inlineStr"/>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>Case : stb box issue   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
@@ -4034,10 +4024,8 @@
           <t>Shreya Acharya</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>9852030441</t>
-        </is>
+      <c r="O16" s="3" t="n">
+        <v>9852030441</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
@@ -4127,10 +4115,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN16" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
@@ -4141,35 +4127,467 @@
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 21m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS16" s="3" t="inlineStr">
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX16" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 11:50 AM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : router change   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>router change</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351189</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Raj Shah</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Raj Shah</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>9814823588</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 11:50:07 AM</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>LTP9814823588</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:10:49 AM</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 11:50:07 AM</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>Gwarko Chowk, Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr">
+        <is>
+          <t>test@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr">
+        <is>
+          <t>10:40 hour</t>
+        </is>
+      </c>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Praktisha Subedi</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>L114-7A</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>Case : router change   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT16" s="3" t="inlineStr">
-        <is>
-          <t>1d 23h 21m</t>
-        </is>
-      </c>
-      <c r="AU16" s="3" t="inlineStr">
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>1d 39m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV16" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW16" s="3" t="inlineStr">
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : router change   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX17" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 11:50 AM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>upgrade wifi 6</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350302</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Niranjan Joshi</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Niranjan Joshi</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>9865762084</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 11:50:47 AM</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>9865762084</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 03:55:30 PM</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 11:50:47 AM</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr">
+        <is>
+          <t>27.663883</t>
+        </is>
+      </c>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA18" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC18" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr">
+        <is>
+          <t>Near Harsha Chowk,Thimi-Biruwa Rd, Anantalingeshwar - Bhaktapur Municipality, Bhaktapur, Bagmati, Ce</t>
+        </is>
+      </c>
+      <c r="AF18" s="3" t="inlineStr">
+        <is>
+          <t>niranjanj455@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG18" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr">
+        <is>
+          <t>15:55 hour</t>
+        </is>
+      </c>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>1,7</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr">
+        <is>
+          <t>85.390102</t>
+        </is>
+      </c>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>1d 19h 55m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX16" s="3" t="inlineStr">
+      <c r="AX18" s="3" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -568,10 +568,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="C8" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="C8" s="4" t="n">
-        <v>14</v>
-      </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>82.4%</t>
+          <t>85.0%</t>
         </is>
       </c>
     </row>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>92.9%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -818,13 +818,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>2</v>
@@ -836,7 +836,7 @@
         <v>2</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -930,13 +930,13 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>3</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>4</v>
@@ -948,7 +948,7 @@
         <v>3</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -962,7 +962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX18"/>
+  <dimension ref="A1:AX21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -4228,10 +4228,8 @@
           <t>Raj Shah</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>9814823588</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v>9814823588</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -4266,10 +4264,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y17" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y17" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
@@ -4325,25 +4321,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN17" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
           <t>L114-7A</t>
         </is>
       </c>
-      <c r="AP17" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP17" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>Case : router change   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
@@ -4444,10 +4436,8 @@
           <t>Niranjan Joshi</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>9865762084</t>
-        </is>
+      <c r="O18" s="3" t="n">
+        <v>9865762084</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
@@ -4482,10 +4472,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y18" s="3" t="inlineStr">
-        <is>
-          <t>27.663883</t>
-        </is>
+      <c r="Y18" s="3" t="n">
+        <v>27.663883</v>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
@@ -4541,55 +4529,699 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN18" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
           <t>1,7</t>
         </is>
       </c>
-      <c r="AP18" s="3" t="inlineStr">
-        <is>
-          <t>85.390102</t>
-        </is>
+      <c r="AP18" s="3" t="n">
+        <v>85.390102</v>
       </c>
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>1d 19h 55m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
           <t>Case : upgrade wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS18" s="3" t="inlineStr">
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX18" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 12:04 PM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>Router upgrade</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351714</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Shubam Bhujel</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Shubam Bhujel</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>9851283087</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 12:04:29 PM</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>9851283087</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:56:38 PM</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 12:04:29 PM</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr">
+        <is>
+          <t>27.6784</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA19" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr">
+        <is>
+          <t>Near Sangam Dairy,Koteshwor-35,Ring-road,Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF19" s="3" t="inlineStr">
+        <is>
+          <t>shubhambhujel12@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG19" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr">
+        <is>
+          <t>05:08 hour</t>
+        </is>
+      </c>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr">
+        <is>
+          <t>Gaurab Dahal</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr">
+        <is>
+          <t>85.34777</t>
+        </is>
+      </c>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT18" s="3" t="inlineStr">
-        <is>
-          <t>1d 19h 55m</t>
-        </is>
-      </c>
-      <c r="AU18" s="3" t="inlineStr">
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>19h 7m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV18" s="3" t="inlineStr">
-        <is>
-          <t>Case : upgrade wifi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW18" s="3" t="inlineStr">
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX19" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 12:11 PM</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352128</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Krishna Tandukar</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Krishna Tandukar</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>9860468102</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 07:39:43 AM</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>9860468102</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 07:39:43 AM</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 12:11:05 PM</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr">
+        <is>
+          <t>27.69104</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA20" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC20" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD20" s="3" t="inlineStr"/>
+      <c r="AE20" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur, Gusingal, near at Computer and Laptop Assecories , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF20" s="3" t="inlineStr">
+        <is>
+          <t>raojinatandukar398@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG20" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH20" s="3" t="inlineStr"/>
+      <c r="AI20" s="3" t="inlineStr">
+        <is>
+          <t>02:10 hour</t>
+        </is>
+      </c>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM20" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>1,10</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr">
+        <is>
+          <t>85.30797</t>
+        </is>
+      </c>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>4h 31m</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>4h 31m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX18" s="3" t="inlineStr">
-        <is>
-          <t>Shashikant Chaudhary</t>
+      <c r="AX20" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 12:10 PM</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352128</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Krishna Tandukar</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Krishna Tandukar</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>9860468102</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 07:39:43 AM</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>9860468102</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 07:39:43 AM</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 12:11:05 PM</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr">
+        <is>
+          <t>27.69104</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur, Gusingal, near at Computer and Laptop Assecories , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF21" s="3" t="inlineStr">
+        <is>
+          <t>raojinatandukar398@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG21" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr">
+        <is>
+          <t>02:10 hour</t>
+        </is>
+      </c>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>1,10</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr">
+        <is>
+          <t>85.30797</t>
+        </is>
+      </c>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>4h 31m</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>4h 31m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX21" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>76.0%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.0%</t>
         </is>
       </c>
     </row>
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>92.9%</t>
+          <t>93.8%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>64.0%</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>3</v>
@@ -833,10 +833,10 @@
         <v>3</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>3</v>
@@ -945,10 +945,10 @@
         <v>3</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -962,7 +962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX21"/>
+  <dimension ref="A1:AX26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -4634,20 +4634,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M19" s="3" t="inlineStr"/>
       <c r="N19" s="3" t="inlineStr">
         <is>
           <t>Shubam Bhujel</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>9851283087</t>
-        </is>
+      <c r="O19" s="3" t="n">
+        <v>9851283087</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
@@ -4682,10 +4676,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y19" s="3" t="inlineStr">
-        <is>
-          <t>27.6784</t>
-        </is>
+      <c r="Y19" s="3" t="n">
+        <v>27.6784</v>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
@@ -4741,25 +4733,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN19" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
           <t>1,5</t>
         </is>
       </c>
-      <c r="AP19" s="3" t="inlineStr">
-        <is>
-          <t>85.34777</t>
-        </is>
+      <c r="AP19" s="3" t="n">
+        <v>85.34777</v>
       </c>
       <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>Case : Router upgrade   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
@@ -4860,10 +4848,8 @@
           <t>Krishna Tandukar</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>9860468102</t>
-        </is>
+      <c r="O20" s="3" t="n">
+        <v>9860468102</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
@@ -4898,10 +4884,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y20" s="3" t="inlineStr">
-        <is>
-          <t>27.69104</t>
-        </is>
+      <c r="Y20" s="3" t="n">
+        <v>27.69104</v>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
@@ -4957,25 +4941,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN20" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
           <t>1,10</t>
         </is>
       </c>
-      <c r="AP20" s="3" t="inlineStr">
-        <is>
-          <t>85.30797</t>
-        </is>
+      <c r="AP20" s="3" t="n">
+        <v>85.30797</v>
       </c>
       <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
@@ -5076,10 +5056,8 @@
           <t>Krishna Tandukar</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>9860468102</t>
-        </is>
+      <c r="O21" s="3" t="n">
+        <v>9860468102</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
@@ -5114,10 +5092,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y21" s="3" t="inlineStr">
-        <is>
-          <t>27.69104</t>
-        </is>
+      <c r="Y21" s="3" t="n">
+        <v>27.69104</v>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
@@ -5173,55 +5149,811 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN21" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
           <t>1,10</t>
         </is>
       </c>
-      <c r="AP21" s="3" t="inlineStr">
-        <is>
-          <t>85.30797</t>
-        </is>
+      <c r="AP21" s="3" t="n">
+        <v>85.30797</v>
       </c>
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>4h 31m</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>4h 31m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS21" s="3" t="inlineStr">
-        <is>
-          <t>4h 31m</t>
-        </is>
-      </c>
-      <c r="AT21" s="3" t="inlineStr">
-        <is>
-          <t>4h 31m</t>
-        </is>
-      </c>
-      <c r="AU21" s="3" t="inlineStr">
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX21" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 12:30 PM</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr"/>
+      <c r="J22" s="3" t="inlineStr"/>
+      <c r="K22" s="3" t="inlineStr"/>
+      <c r="L22" s="3" t="inlineStr"/>
+      <c r="M22" s="3" t="inlineStr"/>
+      <c r="N22" s="3" t="inlineStr"/>
+      <c r="O22" s="3" t="inlineStr"/>
+      <c r="P22" s="3" t="inlineStr"/>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr"/>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr"/>
+      <c r="V22" s="3" t="inlineStr"/>
+      <c r="W22" s="3" t="inlineStr"/>
+      <c r="X22" s="3" t="inlineStr"/>
+      <c r="Y22" s="3" t="inlineStr"/>
+      <c r="Z22" s="3" t="inlineStr"/>
+      <c r="AA22" s="3" t="inlineStr"/>
+      <c r="AB22" s="3" t="inlineStr"/>
+      <c r="AC22" s="3" t="inlineStr"/>
+      <c r="AD22" s="3" t="inlineStr"/>
+      <c r="AE22" s="3" t="inlineStr"/>
+      <c r="AF22" s="3" t="inlineStr"/>
+      <c r="AG22" s="3" t="inlineStr"/>
+      <c r="AH22" s="3" t="inlineStr"/>
+      <c r="AI22" s="3" t="inlineStr"/>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr"/>
+      <c r="AM22" s="3" t="inlineStr"/>
+      <c r="AN22" s="3" t="inlineStr"/>
+      <c r="AO22" s="3" t="inlineStr"/>
+      <c r="AP22" s="3" t="inlineStr"/>
+      <c r="AQ22" s="3" t="inlineStr"/>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW22" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX22" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 12:23 PM</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr"/>
+      <c r="J23" s="3" t="inlineStr"/>
+      <c r="K23" s="3" t="inlineStr"/>
+      <c r="L23" s="3" t="inlineStr"/>
+      <c r="M23" s="3" t="inlineStr"/>
+      <c r="N23" s="3" t="inlineStr"/>
+      <c r="O23" s="3" t="inlineStr"/>
+      <c r="P23" s="3" t="inlineStr"/>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr"/>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="3" t="inlineStr"/>
+      <c r="U23" s="3" t="inlineStr"/>
+      <c r="V23" s="3" t="inlineStr"/>
+      <c r="W23" s="3" t="inlineStr"/>
+      <c r="X23" s="3" t="inlineStr"/>
+      <c r="Y23" s="3" t="inlineStr"/>
+      <c r="Z23" s="3" t="inlineStr"/>
+      <c r="AA23" s="3" t="inlineStr"/>
+      <c r="AB23" s="3" t="inlineStr"/>
+      <c r="AC23" s="3" t="inlineStr"/>
+      <c r="AD23" s="3" t="inlineStr"/>
+      <c r="AE23" s="3" t="inlineStr"/>
+      <c r="AF23" s="3" t="inlineStr"/>
+      <c r="AG23" s="3" t="inlineStr"/>
+      <c r="AH23" s="3" t="inlineStr"/>
+      <c r="AI23" s="3" t="inlineStr"/>
+      <c r="AJ23" s="3" t="inlineStr"/>
+      <c r="AK23" s="3" t="inlineStr"/>
+      <c r="AL23" s="3" t="inlineStr"/>
+      <c r="AM23" s="3" t="inlineStr"/>
+      <c r="AN23" s="3" t="inlineStr"/>
+      <c r="AO23" s="3" t="inlineStr"/>
+      <c r="AP23" s="3" t="inlineStr"/>
+      <c r="AQ23" s="3" t="inlineStr"/>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX23" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 12:20 PM</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr"/>
+      <c r="J24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="inlineStr"/>
+      <c r="L24" s="3" t="inlineStr"/>
+      <c r="M24" s="3" t="inlineStr"/>
+      <c r="N24" s="3" t="inlineStr"/>
+      <c r="O24" s="3" t="inlineStr"/>
+      <c r="P24" s="3" t="inlineStr"/>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr"/>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr"/>
+      <c r="V24" s="3" t="inlineStr"/>
+      <c r="W24" s="3" t="inlineStr"/>
+      <c r="X24" s="3" t="inlineStr"/>
+      <c r="Y24" s="3" t="inlineStr"/>
+      <c r="Z24" s="3" t="inlineStr"/>
+      <c r="AA24" s="3" t="inlineStr"/>
+      <c r="AB24" s="3" t="inlineStr"/>
+      <c r="AC24" s="3" t="inlineStr"/>
+      <c r="AD24" s="3" t="inlineStr"/>
+      <c r="AE24" s="3" t="inlineStr"/>
+      <c r="AF24" s="3" t="inlineStr"/>
+      <c r="AG24" s="3" t="inlineStr"/>
+      <c r="AH24" s="3" t="inlineStr"/>
+      <c r="AI24" s="3" t="inlineStr"/>
+      <c r="AJ24" s="3" t="inlineStr"/>
+      <c r="AK24" s="3" t="inlineStr"/>
+      <c r="AL24" s="3" t="inlineStr"/>
+      <c r="AM24" s="3" t="inlineStr"/>
+      <c r="AN24" s="3" t="inlineStr"/>
+      <c r="AO24" s="3" t="inlineStr"/>
+      <c r="AP24" s="3" t="inlineStr"/>
+      <c r="AQ24" s="3" t="inlineStr"/>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX24" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 12:18 PM</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351421</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Preeti Bajracharya</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>Preeti Bajracharya</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>9841384000</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:28:30 PM</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>9841384000</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:28:30 PM</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 12:20:40 PM</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t>27.69575</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA25" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC25" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD25" s="3" t="inlineStr"/>
+      <c r="AE25" s="3" t="inlineStr">
+        <is>
+          <t>Teku Pachali Galli, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF25" s="3" t="inlineStr">
+        <is>
+          <t>preetibajracharya@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG25" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH25" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI25" s="3" t="inlineStr">
+        <is>
+          <t>08:50 hour</t>
+        </is>
+      </c>
+      <c r="AJ25" s="3" t="inlineStr"/>
+      <c r="AK25" s="3" t="inlineStr"/>
+      <c r="AL25" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO25" s="3" t="inlineStr">
+        <is>
+          <t>CDB044</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr">
+        <is>
+          <t>85.30426</t>
+        </is>
+      </c>
+      <c r="AQ25" s="3" t="inlineStr"/>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>22h 52m</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>22h 52m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="AV21" s="3" t="inlineStr">
+      <c r="AV25" s="3" t="inlineStr">
         <is>
           <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AW21" s="3" t="inlineStr">
+      <c r="AW25" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX21" s="3" t="inlineStr">
+      <c r="AX25" s="3" t="inlineStr">
         <is>
           <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 12:20 PM</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1349414</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>Ajita Pokhrel</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>Ajita Pokhrel</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>9767478420</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 09:01:24 AM</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr"/>
+      <c r="T26" s="3" t="inlineStr"/>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t>9851116870</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 09:01:24 AM</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 12:20:31 PM</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr">
+        <is>
+          <t>27.69699</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA26" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB26" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC26" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD26" s="3" t="inlineStr"/>
+      <c r="AE26" s="3" t="inlineStr">
+        <is>
+          <t>Kalanki kasthamandap college - -(-)-Lead, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF26" s="3" t="inlineStr">
+        <is>
+          <t>pokhrelajita@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG26" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH26" s="3" t="inlineStr"/>
+      <c r="AI26" s="3" t="inlineStr">
+        <is>
+          <t>22:20 hour</t>
+        </is>
+      </c>
+      <c r="AJ26" s="3" t="inlineStr"/>
+      <c r="AK26" s="3" t="inlineStr"/>
+      <c r="AL26" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM26" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN26" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO26" s="3" t="inlineStr">
+        <is>
+          <t>3,8</t>
+        </is>
+      </c>
+      <c r="AP26" s="3" t="inlineStr">
+        <is>
+          <t>85.28057</t>
+        </is>
+      </c>
+      <c r="AQ26" s="3" t="inlineStr"/>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>2d 3h 19m</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>2d 3h 19m</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV26" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW26" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX26" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>4</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>19</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>76.0%</t>
+          <t>73.1%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>15.4%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>61.5%</t>
         </is>
       </c>
     </row>
@@ -962,7 +962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX26"/>
+  <dimension ref="A1:AX27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1008,7 +1008,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -5588,10 +5588,8 @@
           <t>Preeti Bajracharya</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>9841384000</t>
-        </is>
+      <c r="O25" s="3" t="n">
+        <v>9841384000</v>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
@@ -5626,10 +5624,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y25" s="3" t="inlineStr">
-        <is>
-          <t>27.69575</t>
-        </is>
+      <c r="Y25" s="3" t="n">
+        <v>27.69575</v>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
@@ -5667,10 +5663,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH25" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH25" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI25" s="3" t="inlineStr">
         <is>
@@ -5689,25 +5683,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN25" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
           <t>CDB044</t>
         </is>
       </c>
-      <c r="AP25" s="3" t="inlineStr">
-        <is>
-          <t>85.30426</t>
-        </is>
+      <c r="AP25" s="3" t="n">
+        <v>85.30426</v>
       </c>
       <c r="AQ25" s="3" t="inlineStr"/>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
@@ -5808,10 +5798,8 @@
           <t>Ajita Pokhrel</t>
         </is>
       </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t>9767478420</t>
-        </is>
+      <c r="O26" s="3" t="n">
+        <v>9767478420</v>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
@@ -5846,10 +5834,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y26" s="3" t="inlineStr">
-        <is>
-          <t>27.69699</t>
-        </is>
+      <c r="Y26" s="3" t="n">
+        <v>27.69699</v>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
@@ -5905,47 +5891,43 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN26" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN26" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
           <t>3,8</t>
         </is>
       </c>
-      <c r="AP26" s="3" t="inlineStr">
-        <is>
-          <t>85.28057</t>
-        </is>
+      <c r="AP26" s="3" t="n">
+        <v>85.28057</v>
       </c>
       <c r="AQ26" s="3" t="inlineStr"/>
       <c r="AR26" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>2d 3h 19m</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>2d 3h 19m</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV26" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS26" s="3" t="inlineStr">
-        <is>
-          <t>2d 3h 19m</t>
-        </is>
-      </c>
-      <c r="AT26" s="3" t="inlineStr">
-        <is>
-          <t>2d 3h 19m</t>
-        </is>
-      </c>
-      <c r="AU26" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV26" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW26" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -5954,6 +5936,114 @@
       <c r="AX26" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 12:44 PM</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr"/>
+      <c r="J27" s="3" t="inlineStr"/>
+      <c r="K27" s="3" t="inlineStr"/>
+      <c r="L27" s="3" t="inlineStr"/>
+      <c r="M27" s="3" t="inlineStr"/>
+      <c r="N27" s="3" t="inlineStr"/>
+      <c r="O27" s="3" t="inlineStr"/>
+      <c r="P27" s="3" t="inlineStr"/>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr"/>
+      <c r="S27" s="3" t="inlineStr"/>
+      <c r="T27" s="3" t="inlineStr"/>
+      <c r="U27" s="3" t="inlineStr"/>
+      <c r="V27" s="3" t="inlineStr"/>
+      <c r="W27" s="3" t="inlineStr"/>
+      <c r="X27" s="3" t="inlineStr"/>
+      <c r="Y27" s="3" t="inlineStr"/>
+      <c r="Z27" s="3" t="inlineStr"/>
+      <c r="AA27" s="3" t="inlineStr"/>
+      <c r="AB27" s="3" t="inlineStr"/>
+      <c r="AC27" s="3" t="inlineStr"/>
+      <c r="AD27" s="3" t="inlineStr"/>
+      <c r="AE27" s="3" t="inlineStr"/>
+      <c r="AF27" s="3" t="inlineStr"/>
+      <c r="AG27" s="3" t="inlineStr"/>
+      <c r="AH27" s="3" t="inlineStr"/>
+      <c r="AI27" s="3" t="inlineStr"/>
+      <c r="AJ27" s="3" t="inlineStr"/>
+      <c r="AK27" s="3" t="inlineStr"/>
+      <c r="AL27" s="3" t="inlineStr"/>
+      <c r="AM27" s="3" t="inlineStr"/>
+      <c r="AN27" s="3" t="inlineStr"/>
+      <c r="AO27" s="3" t="inlineStr"/>
+      <c r="AP27" s="3" t="inlineStr"/>
+      <c r="AQ27" s="3" t="inlineStr"/>
+      <c r="AR27" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW27" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX27" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>75.9%</t>
         </is>
       </c>
     </row>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>17.2%</t>
         </is>
       </c>
     </row>
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>93.8%</t>
+          <t>94.4%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>62.1%</t>
         </is>
       </c>
     </row>
@@ -824,19 +824,19 @@
         <v>3</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>3</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -936,19 +936,19 @@
         <v>3</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>4</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>4</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -962,7 +962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX27"/>
+  <dimension ref="A1:AX30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1008,7 +1008,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -6047,6 +6047,634 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 12:53 PM</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351515</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>Bishal Tamrakar</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>Bishal Tamrakar</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>9808812245</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 12:53:34 PM</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr"/>
+      <c r="T28" s="3" t="inlineStr"/>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t>9808812245</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 02:33:48 PM</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 12:53:34 PM</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr"/>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA28" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB28" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC28" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD28" s="3" t="inlineStr"/>
+      <c r="AE28" s="3" t="inlineStr">
+        <is>
+          <t>Near Bhaktapur Municipal - 6 No.Ward Office, MCFJ+RMM, Bholachhen - Yachhen Rd, Bhaktapur 44800, Bag</t>
+        </is>
+      </c>
+      <c r="AF28" s="3" t="inlineStr">
+        <is>
+          <t>tamrakarbishal905@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG28" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH28" s="3" t="inlineStr"/>
+      <c r="AI28" s="3" t="inlineStr">
+        <is>
+          <t>08:20 hour</t>
+        </is>
+      </c>
+      <c r="AJ28" s="3" t="inlineStr"/>
+      <c r="AK28" s="3" t="inlineStr"/>
+      <c r="AL28" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM28" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN28" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO28" s="3" t="inlineStr">
+        <is>
+          <t>L37-1</t>
+        </is>
+      </c>
+      <c r="AP28" s="3" t="inlineStr"/>
+      <c r="AQ28" s="3" t="inlineStr"/>
+      <c r="AR28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>22h 19m</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW28" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX28" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 12:58 PM</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>TKT1349431</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>Kundan Mishra</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>Kundan Mishra</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>9861396664</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 12:58:55 PM</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr"/>
+      <c r="T29" s="3" t="inlineStr"/>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>BKT9861396664</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 09:14:25 AM</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 12:58:55 PM</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="inlineStr"/>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA29" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB29" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC29" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD29" s="3" t="inlineStr"/>
+      <c r="AE29" s="3" t="inlineStr">
+        <is>
+          <t>Nagadesh Health Post - Health consultant M9PP+27J Madhyapur Thimi 44600, Bhaktapur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF29" s="3" t="inlineStr">
+        <is>
+          <t>mishrakundan8108@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG29" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH29" s="3" t="inlineStr"/>
+      <c r="AI29" s="3" t="inlineStr">
+        <is>
+          <t>22:58 hour</t>
+        </is>
+      </c>
+      <c r="AJ29" s="3" t="inlineStr"/>
+      <c r="AK29" s="3" t="inlineStr"/>
+      <c r="AL29" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM29" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN29" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO29" s="3" t="inlineStr">
+        <is>
+          <t>3,3</t>
+        </is>
+      </c>
+      <c r="AP29" s="3" t="inlineStr"/>
+      <c r="AQ29" s="3" t="inlineStr"/>
+      <c r="AR29" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>2d 3h 44m</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW29" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX29" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 12:47 PM</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344315</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>Purnima Tamang</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>Purnima Tamang</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>9803233369</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 12:47:27 PM</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr"/>
+      <c r="T30" s="3" t="inlineStr"/>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t>9803233369</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 10:07:51 PM</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 12:47:27 PM</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="inlineStr">
+        <is>
+          <t>27.687687</t>
+        </is>
+      </c>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA30" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB30" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC30" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD30" s="3" t="inlineStr"/>
+      <c r="AE30" s="3" t="inlineStr">
+        <is>
+          <t>Madhyapur Thimi, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF30" s="3" t="inlineStr"/>
+      <c r="AG30" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH30" s="3" t="inlineStr"/>
+      <c r="AI30" s="3" t="inlineStr">
+        <is>
+          <t>04:47 hour</t>
+        </is>
+      </c>
+      <c r="AJ30" s="3" t="inlineStr"/>
+      <c r="AK30" s="3" t="inlineStr"/>
+      <c r="AL30" s="3" t="inlineStr">
+        <is>
+          <t>Pratik Shrestha</t>
+        </is>
+      </c>
+      <c r="AM30" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO30" s="3" t="inlineStr">
+        <is>
+          <t>L18-5</t>
+        </is>
+      </c>
+      <c r="AP30" s="3" t="inlineStr">
+        <is>
+          <t>85.386824</t>
+        </is>
+      </c>
+      <c r="AQ30" s="3" t="inlineStr"/>
+      <c r="AR30" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>6d 14h 39m</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX30" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
@@ -1008,7 +1008,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -6114,10 +6114,8 @@
           <t>Bishal Tamrakar</t>
         </is>
       </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t>9808812245</t>
-        </is>
+      <c r="O28" s="3" t="n">
+        <v>9808812245</v>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
@@ -6207,10 +6205,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN28" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN28" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
@@ -6221,7 +6217,7 @@
       <c r="AQ28" s="3" t="inlineStr"/>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
@@ -6322,10 +6318,8 @@
           <t>Kundan Mishra</t>
         </is>
       </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>9861396664</t>
-        </is>
+      <c r="O29" s="3" t="n">
+        <v>9861396664</v>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
@@ -6415,10 +6409,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN29" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN29" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
@@ -6429,7 +6421,7 @@
       <c r="AQ29" s="3" t="inlineStr"/>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
@@ -6530,10 +6522,8 @@
           <t>Purnima Tamang</t>
         </is>
       </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>9803233369</t>
-        </is>
+      <c r="O30" s="3" t="n">
+        <v>9803233369</v>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
@@ -6568,10 +6558,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y30" s="3" t="inlineStr">
-        <is>
-          <t>27.687687</t>
-        </is>
+      <c r="Y30" s="3" t="n">
+        <v>27.687687</v>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
@@ -6623,25 +6611,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN30" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
           <t>L18-5</t>
         </is>
       </c>
-      <c r="AP30" s="3" t="inlineStr">
-        <is>
-          <t>85.386824</t>
-        </is>
+      <c r="AP30" s="3" t="n">
+        <v>85.386824</v>
       </c>
       <c r="AQ30" s="3" t="inlineStr"/>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>5</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C7" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>18.8%</t>
         </is>
       </c>
     </row>
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>17</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>94.4%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -756,10 +756,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -818,7 +818,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>3</v>
@@ -833,10 +833,10 @@
         <v>4</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -924,31 +924,59 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Specific Website/App is slow</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" s="4" t="n">
+      <c r="D7" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F6" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>22</v>
+      <c r="G7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -962,7 +990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX30"/>
+  <dimension ref="A1:AX33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -975,10 +1003,10 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="32" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="32" customWidth="1" min="14" max="14"/>
+    <col width="34" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -997,7 +1025,7 @@
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
     <col width="31" customWidth="1" min="32" max="32"/>
-    <col width="28" customWidth="1" min="33" max="33"/>
+    <col width="31" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -1008,7 +1036,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -6659,6 +6687,634 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 1:25 PM</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350037</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>S K Mustafa</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>S K Mustafa</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>9818066040</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 01:58:27 PM</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="3" t="inlineStr"/>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t>9818066040</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 01:58:27 PM</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 01:25:06 PM</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y31" s="3" t="inlineStr">
+        <is>
+          <t>27.707037</t>
+        </is>
+      </c>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA31" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB31" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC31" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD31" s="3" t="inlineStr"/>
+      <c r="AE31" s="3" t="inlineStr">
+        <is>
+          <t>Nera Jagat Sundar Bwonekuthi Secondary School,P842+XPF, ????????? ?????? ???, Kathmandu 44600, Bagma</t>
+        </is>
+      </c>
+      <c r="AF31" s="3" t="inlineStr">
+        <is>
+          <t>ali.sksabir@yahoo.com</t>
+        </is>
+      </c>
+      <c r="AG31" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH31" s="3" t="inlineStr"/>
+      <c r="AI31" s="3" t="inlineStr"/>
+      <c r="AJ31" s="3" t="inlineStr"/>
+      <c r="AK31" s="3" t="inlineStr"/>
+      <c r="AL31" s="3" t="inlineStr">
+        <is>
+          <t>Indra KC</t>
+        </is>
+      </c>
+      <c r="AM31" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO31" s="3" t="inlineStr">
+        <is>
+          <t>1,12</t>
+        </is>
+      </c>
+      <c r="AP31" s="3" t="inlineStr">
+        <is>
+          <t>85.301797</t>
+        </is>
+      </c>
+      <c r="AQ31" s="3" t="inlineStr"/>
+      <c r="AR31" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 26m</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 26m</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW31" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX31" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 1:19 PM</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : no internet connection  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>no internet connection</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352367</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>Hotel Tulsi Sagar Int'l Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>Hotel Tulsi Sagar Int'l Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>9708426461</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 01:19:01 PM</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="3" t="inlineStr"/>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t>KLK9708426461</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 10:43:13 AM</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 01:19:01 PM</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr"/>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA32" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB32" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC32" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD32" s="3" t="inlineStr"/>
+      <c r="AE32" s="3" t="inlineStr">
+        <is>
+          <t>????????-??, ???????? ??? ?????, Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF32" s="3" t="inlineStr">
+        <is>
+          <t>014957592@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG32" s="3" t="inlineStr">
+        <is>
+          <t>Specific Website/App is slow</t>
+        </is>
+      </c>
+      <c r="AH32" s="3" t="inlineStr"/>
+      <c r="AI32" s="3" t="inlineStr">
+        <is>
+          <t>02:36 hour</t>
+        </is>
+      </c>
+      <c r="AJ32" s="3" t="inlineStr"/>
+      <c r="AK32" s="3" t="inlineStr"/>
+      <c r="AL32" s="3" t="inlineStr">
+        <is>
+          <t>Aashna Pulami</t>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO32" s="3" t="inlineStr">
+        <is>
+          <t>1,6</t>
+        </is>
+      </c>
+      <c r="AP32" s="3" t="inlineStr"/>
+      <c r="AQ32" s="3" t="inlineStr"/>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>Case : no internet connection  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>2h 35m</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
+          <t>Case : no internet connection  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX32" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 1:11 PM</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351874</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>binisha Bomjan</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>binisha Bomjan</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>9808801236</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 06:51:07 PM</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr"/>
+      <c r="T33" s="3" t="inlineStr"/>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t>KLK9808801236</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 06:51:07 PM</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 01:11:33 PM</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y33" s="3" t="inlineStr"/>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA33" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB33" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC33" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD33" s="3" t="inlineStr"/>
+      <c r="AE33" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu Swoyambhu ward no:15 Badegal near Arunodaya School - Kathmandu Metropolitan, Kathmandu, Ba</t>
+        </is>
+      </c>
+      <c r="AF33" s="3" t="inlineStr">
+        <is>
+          <t>9828745746@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG33" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH33" s="3" t="inlineStr"/>
+      <c r="AI33" s="3" t="inlineStr">
+        <is>
+          <t>04:20 hour</t>
+        </is>
+      </c>
+      <c r="AJ33" s="3" t="inlineStr"/>
+      <c r="AK33" s="3" t="inlineStr"/>
+      <c r="AL33" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO33" s="3" t="inlineStr">
+        <is>
+          <t>CDB234</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr"/>
+      <c r="AQ33" s="3" t="inlineStr"/>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>18h 20m</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>18h 20m</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW33" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX33" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>4</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>24</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>72.7%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>18.2%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>60.6%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX33"/>
+  <dimension ref="A1:AX34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1036,7 +1036,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -6754,10 +6754,8 @@
           <t>S K Mustafa</t>
         </is>
       </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>9818066040</t>
-        </is>
+      <c r="O31" s="3" t="n">
+        <v>9818066040</v>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
@@ -6792,10 +6790,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y31" s="3" t="inlineStr">
-        <is>
-          <t>27.707037</t>
-        </is>
+      <c r="Y31" s="3" t="n">
+        <v>27.707037</v>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
@@ -6847,25 +6843,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN31" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN31" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
           <t>1,12</t>
         </is>
       </c>
-      <c r="AP31" s="3" t="inlineStr">
-        <is>
-          <t>85.301797</t>
-        </is>
+      <c r="AP31" s="3" t="n">
+        <v>85.30179699999999</v>
       </c>
       <c r="AQ31" s="3" t="inlineStr"/>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
@@ -6966,10 +6958,8 @@
           <t>Hotel Tulsi Sagar Int'l Pvt Ltd</t>
         </is>
       </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t>9708426461</t>
-        </is>
+      <c r="O32" s="3" t="n">
+        <v>9708426461</v>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
@@ -7059,10 +7049,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN32" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
@@ -7073,7 +7061,7 @@
       <c r="AQ32" s="3" t="inlineStr"/>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>Case : no internet connection  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
@@ -7174,10 +7162,8 @@
           <t>binisha Bomjan</t>
         </is>
       </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>9808801236</t>
-        </is>
+      <c r="O33" s="3" t="n">
+        <v>9808801236</v>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
@@ -7267,10 +7253,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN33" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
@@ -7281,29 +7265,29 @@
       <c r="AQ33" s="3" t="inlineStr"/>
       <c r="AR33" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>18h 20m</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>18h 20m</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS33" s="3" t="inlineStr">
-        <is>
-          <t>18h 20m</t>
-        </is>
-      </c>
-      <c r="AT33" s="3" t="inlineStr">
-        <is>
-          <t>18h 20m</t>
-        </is>
-      </c>
-      <c r="AU33" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV33" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW33" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -7312,6 +7296,114 @@
       <c r="AX33" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 1:33 PM</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr"/>
+      <c r="J34" s="3" t="inlineStr"/>
+      <c r="K34" s="3" t="inlineStr"/>
+      <c r="L34" s="3" t="inlineStr"/>
+      <c r="M34" s="3" t="inlineStr"/>
+      <c r="N34" s="3" t="inlineStr"/>
+      <c r="O34" s="3" t="inlineStr"/>
+      <c r="P34" s="3" t="inlineStr"/>
+      <c r="Q34" s="3" t="inlineStr"/>
+      <c r="R34" s="3" t="inlineStr"/>
+      <c r="S34" s="3" t="inlineStr"/>
+      <c r="T34" s="3" t="inlineStr"/>
+      <c r="U34" s="3" t="inlineStr"/>
+      <c r="V34" s="3" t="inlineStr"/>
+      <c r="W34" s="3" t="inlineStr"/>
+      <c r="X34" s="3" t="inlineStr"/>
+      <c r="Y34" s="3" t="inlineStr"/>
+      <c r="Z34" s="3" t="inlineStr"/>
+      <c r="AA34" s="3" t="inlineStr"/>
+      <c r="AB34" s="3" t="inlineStr"/>
+      <c r="AC34" s="3" t="inlineStr"/>
+      <c r="AD34" s="3" t="inlineStr"/>
+      <c r="AE34" s="3" t="inlineStr"/>
+      <c r="AF34" s="3" t="inlineStr"/>
+      <c r="AG34" s="3" t="inlineStr"/>
+      <c r="AH34" s="3" t="inlineStr"/>
+      <c r="AI34" s="3" t="inlineStr"/>
+      <c r="AJ34" s="3" t="inlineStr"/>
+      <c r="AK34" s="3" t="inlineStr"/>
+      <c r="AL34" s="3" t="inlineStr"/>
+      <c r="AM34" s="3" t="inlineStr"/>
+      <c r="AN34" s="3" t="inlineStr"/>
+      <c r="AO34" s="3" t="inlineStr"/>
+      <c r="AP34" s="3" t="inlineStr"/>
+      <c r="AQ34" s="3" t="inlineStr"/>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW34" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX34" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>19.4%</t>
         </is>
       </c>
     </row>
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>18</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>61.1%</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>4</v>
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Specific Website/App is slow</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -855,7 +855,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>0</v>
@@ -864,13 +864,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -883,13 +883,13 @@
         <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" s="6" t="n">
         <v>1</v>
@@ -926,7 +926,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Specific Website/App is slow</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -939,13 +939,13 @@
         <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>1</v>
@@ -961,13 +961,13 @@
         <v>4</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>4</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>4</v>
@@ -976,7 +976,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -990,7 +990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX34"/>
+  <dimension ref="A1:AX37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1036,7 +1036,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -7407,6 +7407,630 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 1:55 PM</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Case : CCTV issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>CCTV issue</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351212</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>Prakash Neupane</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>Prakash Neupane</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>9847329472</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 01:55:43 PM</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr"/>
+      <c r="T35" s="3" t="inlineStr"/>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t>KLK9816451459</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:26:51 AM</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 01:55:43 PM</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y35" s="3" t="inlineStr"/>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA35" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB35" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC35" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD35" s="3" t="inlineStr"/>
+      <c r="AE35" s="3" t="inlineStr">
+        <is>
+          <t>QFX Cinemas, City Square Mall QFX Cinemas, City Square Mall - Movie theater P8P9+549 ???????? ??????</t>
+        </is>
+      </c>
+      <c r="AF35" s="3" t="inlineStr">
+        <is>
+          <t>9816451459@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG35" s="3" t="inlineStr">
+        <is>
+          <t>Specific Website/App is slow</t>
+        </is>
+      </c>
+      <c r="AH35" s="3" t="inlineStr"/>
+      <c r="AI35" s="3" t="inlineStr">
+        <is>
+          <t>12:29 hour</t>
+        </is>
+      </c>
+      <c r="AJ35" s="3" t="inlineStr"/>
+      <c r="AK35" s="3" t="inlineStr"/>
+      <c r="AL35" s="3" t="inlineStr">
+        <is>
+          <t>Aashna Pulami</t>
+        </is>
+      </c>
+      <c r="AM35" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO35" s="3" t="inlineStr">
+        <is>
+          <t>L55-1</t>
+        </is>
+      </c>
+      <c r="AP35" s="3" t="inlineStr"/>
+      <c r="AQ35" s="3" t="inlineStr"/>
+      <c r="AR35" s="3" t="inlineStr">
+        <is>
+          <t>Case : CCTV issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 28m</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
+          <t>Case : CCTV issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX35" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 2:00 PM</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>wifi6 upgrade</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352253</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>Mega Hospital Pharmacy</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>Mega Hospital Pharmacy</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>9862483865</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr"/>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 02:00:56 PM</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr"/>
+      <c r="T36" s="3" t="inlineStr"/>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t>LTP9862483865</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 09:55:56 AM</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 02:00:56 PM</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="inlineStr"/>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA36" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB36" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC36" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD36" s="3" t="inlineStr"/>
+      <c r="AE36" s="3" t="inlineStr">
+        <is>
+          <t>Dhobighat , Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF36" s="3" t="inlineStr">
+        <is>
+          <t>Megapharmacy@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG36" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH36" s="3" t="inlineStr"/>
+      <c r="AI36" s="3" t="inlineStr">
+        <is>
+          <t>04:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ36" s="3" t="inlineStr"/>
+      <c r="AK36" s="3" t="inlineStr"/>
+      <c r="AL36" s="3" t="inlineStr">
+        <is>
+          <t>Aashna Pulami</t>
+        </is>
+      </c>
+      <c r="AM36" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN36" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO36" s="3" t="inlineStr">
+        <is>
+          <t>3,5</t>
+        </is>
+      </c>
+      <c r="AP36" s="3" t="inlineStr"/>
+      <c r="AQ36" s="3" t="inlineStr"/>
+      <c r="AR36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>4h 5m</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW36" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX36" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 1:59 PM</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6 Router Upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>wifi6 Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352258</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>Mega Hospital</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>Mega Hospital</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>9849670860</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr"/>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 01:59:02 PM</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr"/>
+      <c r="T37" s="3" t="inlineStr"/>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t>LTP9849670860</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 09:56:54 AM</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 01:59:02 PM</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y37" s="3" t="inlineStr"/>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA37" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB37" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC37" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD37" s="3" t="inlineStr"/>
+      <c r="AE37" s="3" t="inlineStr">
+        <is>
+          <t>Dhobighat, Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF37" s="3" t="inlineStr">
+        <is>
+          <t>info@megahospital.com.np</t>
+        </is>
+      </c>
+      <c r="AG37" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH37" s="3" t="inlineStr"/>
+      <c r="AI37" s="3" t="inlineStr">
+        <is>
+          <t>03:59 hour</t>
+        </is>
+      </c>
+      <c r="AJ37" s="3" t="inlineStr"/>
+      <c r="AK37" s="3" t="inlineStr"/>
+      <c r="AL37" s="3" t="inlineStr">
+        <is>
+          <t>Aashna Pulami</t>
+        </is>
+      </c>
+      <c r="AM37" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO37" s="3" t="inlineStr">
+        <is>
+          <t>3,5</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr"/>
+      <c r="AQ37" s="3" t="inlineStr"/>
+      <c r="AR37" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6 Router Upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>4h 2m</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6 Router Upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW37" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX37" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>6</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>69.0%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>20</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>88.0%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>59.5%</t>
         </is>
       </c>
     </row>
@@ -827,16 +827,16 @@
         <v>4</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -967,16 +967,16 @@
         <v>4</v>
       </c>
       <c r="E7" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="F7" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>5</v>
-      </c>
       <c r="H7" s="4" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -990,7 +990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX37"/>
+  <dimension ref="A1:AX43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1020,7 +1020,7 @@
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
-    <col width="17" customWidth="1" min="28" max="28"/>
+    <col width="21" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
@@ -1039,7 +1039,7 @@
     <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="32" customWidth="1" min="47" max="47"/>
+    <col width="45" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
     <col width="23" customWidth="1" min="50" max="50"/>
@@ -7474,10 +7474,8 @@
           <t>Prakash Neupane</t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>9847329472</t>
-        </is>
+      <c r="O35" s="3" t="n">
+        <v>9847329472</v>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
@@ -7567,10 +7565,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN35" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN35" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
@@ -7581,7 +7577,7 @@
       <c r="AQ35" s="3" t="inlineStr"/>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>Case : CCTV issue  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
@@ -7682,10 +7678,8 @@
           <t>Mega Hospital Pharmacy</t>
         </is>
       </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t>9862483865</t>
-        </is>
+      <c r="O36" s="3" t="n">
+        <v>9862483865</v>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
@@ -7775,10 +7769,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN36" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN36" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
@@ -7789,7 +7781,7 @@
       <c r="AQ36" s="3" t="inlineStr"/>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6 upgrade  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
@@ -7890,10 +7882,8 @@
           <t>Mega Hospital</t>
         </is>
       </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t>9849670860</t>
-        </is>
+      <c r="O37" s="3" t="n">
+        <v>9849670860</v>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
@@ -7983,10 +7973,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN37" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN37" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
@@ -7997,37 +7985,997 @@
       <c r="AQ37" s="3" t="inlineStr"/>
       <c r="AR37" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>4h 2m</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6 Router Upgrade  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS37" s="3" t="inlineStr">
+      <c r="AW37" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX37" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 2:08 PM</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case :  wifi 6 router upgrade  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr"/>
+      <c r="J38" s="3" t="inlineStr"/>
+      <c r="K38" s="3" t="inlineStr"/>
+      <c r="L38" s="3" t="inlineStr"/>
+      <c r="M38" s="3" t="inlineStr"/>
+      <c r="N38" s="3" t="inlineStr"/>
+      <c r="O38" s="3" t="inlineStr"/>
+      <c r="P38" s="3" t="inlineStr"/>
+      <c r="Q38" s="3" t="inlineStr"/>
+      <c r="R38" s="3" t="inlineStr"/>
+      <c r="S38" s="3" t="inlineStr"/>
+      <c r="T38" s="3" t="inlineStr"/>
+      <c r="U38" s="3" t="inlineStr"/>
+      <c r="V38" s="3" t="inlineStr"/>
+      <c r="W38" s="3" t="inlineStr"/>
+      <c r="X38" s="3" t="inlineStr"/>
+      <c r="Y38" s="3" t="inlineStr"/>
+      <c r="Z38" s="3" t="inlineStr"/>
+      <c r="AA38" s="3" t="inlineStr"/>
+      <c r="AB38" s="3" t="inlineStr"/>
+      <c r="AC38" s="3" t="inlineStr"/>
+      <c r="AD38" s="3" t="inlineStr"/>
+      <c r="AE38" s="3" t="inlineStr"/>
+      <c r="AF38" s="3" t="inlineStr"/>
+      <c r="AG38" s="3" t="inlineStr"/>
+      <c r="AH38" s="3" t="inlineStr"/>
+      <c r="AI38" s="3" t="inlineStr"/>
+      <c r="AJ38" s="3" t="inlineStr"/>
+      <c r="AK38" s="3" t="inlineStr"/>
+      <c r="AL38" s="3" t="inlineStr"/>
+      <c r="AM38" s="3" t="inlineStr"/>
+      <c r="AN38" s="3" t="inlineStr"/>
+      <c r="AO38" s="3" t="inlineStr"/>
+      <c r="AP38" s="3" t="inlineStr"/>
+      <c r="AQ38" s="3" t="inlineStr"/>
+      <c r="AR38" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV38" s="3" t="inlineStr">
+        <is>
+          <t>Case :  wifi 6 router upgrade  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW38" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX38" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 2:03 PM</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6 upgrade  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352151</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>Shreyak Timsina</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>Follow Up</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>Shreyak Timsina</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>9863626262</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr"/>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 02:03:49 PM</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr"/>
+      <c r="T39" s="3" t="inlineStr"/>
+      <c r="U39" s="3" t="inlineStr">
+        <is>
+          <t>9863626262</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 08:09:26 AM</t>
+        </is>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 02:03:49 PM</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="inlineStr">
+        <is>
+          <t>27.691212</t>
+        </is>
+      </c>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA39" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB39" s="3" t="inlineStr">
+        <is>
+          <t>MS TICKET  HANDLER</t>
+        </is>
+      </c>
+      <c r="AC39" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD39" s="3" t="inlineStr"/>
+      <c r="AE39" s="3" t="inlineStr">
+        <is>
+          <t>M8RF+FCM, Radha Krishna Marg, Kathmandu 44600,Department of Commerce, Supplies and Consumer Protecti</t>
+        </is>
+      </c>
+      <c r="AF39" s="3" t="inlineStr">
+        <is>
+          <t>shreyaktimsina29@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG39" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH39" s="3" t="inlineStr"/>
+      <c r="AI39" s="3" t="inlineStr"/>
+      <c r="AJ39" s="3" t="inlineStr"/>
+      <c r="AK39" s="3" t="inlineStr"/>
+      <c r="AL39" s="3" t="inlineStr">
+        <is>
+          <t>Aryan Maharjan</t>
+        </is>
+      </c>
+      <c r="AM39" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN39" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO39" s="3" t="inlineStr">
+        <is>
+          <t>2,11</t>
+        </is>
+      </c>
+      <c r="AP39" s="3" t="inlineStr">
+        <is>
+          <t>85.323547</t>
+        </is>
+      </c>
+      <c r="AQ39" s="3" t="inlineStr"/>
+      <c r="AR39" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6 upgrade  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT37" s="3" t="inlineStr">
-        <is>
-          <t>4h 2m</t>
-        </is>
-      </c>
-      <c r="AU37" s="3" t="inlineStr">
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>5h 54m</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
+          <t>Assigned / Transferred to MS / Other Handler</t>
+        </is>
+      </c>
+      <c r="AV39" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6 upgrade  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW39" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX39" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 2:14 PM</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr"/>
+      <c r="J40" s="3" t="inlineStr"/>
+      <c r="K40" s="3" t="inlineStr"/>
+      <c r="L40" s="3" t="inlineStr"/>
+      <c r="M40" s="3" t="inlineStr"/>
+      <c r="N40" s="3" t="inlineStr"/>
+      <c r="O40" s="3" t="inlineStr"/>
+      <c r="P40" s="3" t="inlineStr"/>
+      <c r="Q40" s="3" t="inlineStr"/>
+      <c r="R40" s="3" t="inlineStr"/>
+      <c r="S40" s="3" t="inlineStr"/>
+      <c r="T40" s="3" t="inlineStr"/>
+      <c r="U40" s="3" t="inlineStr"/>
+      <c r="V40" s="3" t="inlineStr"/>
+      <c r="W40" s="3" t="inlineStr"/>
+      <c r="X40" s="3" t="inlineStr"/>
+      <c r="Y40" s="3" t="inlineStr"/>
+      <c r="Z40" s="3" t="inlineStr"/>
+      <c r="AA40" s="3" t="inlineStr"/>
+      <c r="AB40" s="3" t="inlineStr"/>
+      <c r="AC40" s="3" t="inlineStr"/>
+      <c r="AD40" s="3" t="inlineStr"/>
+      <c r="AE40" s="3" t="inlineStr"/>
+      <c r="AF40" s="3" t="inlineStr"/>
+      <c r="AG40" s="3" t="inlineStr"/>
+      <c r="AH40" s="3" t="inlineStr"/>
+      <c r="AI40" s="3" t="inlineStr"/>
+      <c r="AJ40" s="3" t="inlineStr"/>
+      <c r="AK40" s="3" t="inlineStr"/>
+      <c r="AL40" s="3" t="inlineStr"/>
+      <c r="AM40" s="3" t="inlineStr"/>
+      <c r="AN40" s="3" t="inlineStr"/>
+      <c r="AO40" s="3" t="inlineStr"/>
+      <c r="AP40" s="3" t="inlineStr"/>
+      <c r="AQ40" s="3" t="inlineStr"/>
+      <c r="AR40" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS40" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT40" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU40" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW40" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX40" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 2:13 PM</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350997</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>Manita Khadka</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>Manita Khadka</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>9842359754</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr"/>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 02:13:38 PM</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr"/>
+      <c r="T41" s="3" t="inlineStr"/>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t>9842359754</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 09:21:29 AM</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 02:13:38 PM</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y41" s="3" t="inlineStr"/>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA41" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB41" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC41" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD41" s="3" t="inlineStr"/>
+      <c r="AE41" s="3" t="inlineStr">
+        <is>
+          <t>Near Tiger Lily Petting farm - Park Anantalingeshwar, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF41" s="3" t="inlineStr">
+        <is>
+          <t>manitakhadka54@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG41" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH41" s="3" t="inlineStr"/>
+      <c r="AI41" s="3" t="inlineStr">
+        <is>
+          <t>14:13 hour</t>
+        </is>
+      </c>
+      <c r="AJ41" s="3" t="inlineStr"/>
+      <c r="AK41" s="3" t="inlineStr"/>
+      <c r="AL41" s="3" t="inlineStr">
+        <is>
+          <t>Indra KC</t>
+        </is>
+      </c>
+      <c r="AM41" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN41" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO41" s="3" t="inlineStr">
+        <is>
+          <t>L53-8</t>
+        </is>
+      </c>
+      <c r="AP41" s="3" t="inlineStr"/>
+      <c r="AQ41" s="3" t="inlineStr"/>
+      <c r="AR41" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS41" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 52m</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV37" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6 Router Upgrade  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="AW37" s="3" t="inlineStr">
+      <c r="AV41" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW41" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX37" s="3" t="inlineStr">
-        <is>
-          <t>Rajesh Maharjan</t>
+      <c r="AX41" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 2:04 PM</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr"/>
+      <c r="J42" s="3" t="inlineStr"/>
+      <c r="K42" s="3" t="inlineStr"/>
+      <c r="L42" s="3" t="inlineStr"/>
+      <c r="M42" s="3" t="inlineStr"/>
+      <c r="N42" s="3" t="inlineStr"/>
+      <c r="O42" s="3" t="inlineStr"/>
+      <c r="P42" s="3" t="inlineStr"/>
+      <c r="Q42" s="3" t="inlineStr"/>
+      <c r="R42" s="3" t="inlineStr"/>
+      <c r="S42" s="3" t="inlineStr"/>
+      <c r="T42" s="3" t="inlineStr"/>
+      <c r="U42" s="3" t="inlineStr"/>
+      <c r="V42" s="3" t="inlineStr"/>
+      <c r="W42" s="3" t="inlineStr"/>
+      <c r="X42" s="3" t="inlineStr"/>
+      <c r="Y42" s="3" t="inlineStr"/>
+      <c r="Z42" s="3" t="inlineStr"/>
+      <c r="AA42" s="3" t="inlineStr"/>
+      <c r="AB42" s="3" t="inlineStr"/>
+      <c r="AC42" s="3" t="inlineStr"/>
+      <c r="AD42" s="3" t="inlineStr"/>
+      <c r="AE42" s="3" t="inlineStr"/>
+      <c r="AF42" s="3" t="inlineStr"/>
+      <c r="AG42" s="3" t="inlineStr"/>
+      <c r="AH42" s="3" t="inlineStr"/>
+      <c r="AI42" s="3" t="inlineStr"/>
+      <c r="AJ42" s="3" t="inlineStr"/>
+      <c r="AK42" s="3" t="inlineStr"/>
+      <c r="AL42" s="3" t="inlineStr"/>
+      <c r="AM42" s="3" t="inlineStr"/>
+      <c r="AN42" s="3" t="inlineStr"/>
+      <c r="AO42" s="3" t="inlineStr"/>
+      <c r="AP42" s="3" t="inlineStr"/>
+      <c r="AQ42" s="3" t="inlineStr"/>
+      <c r="AR42" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS42" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT42" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU42" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV42" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW42" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX42" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 2:03 PM</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352537</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>Roshlin Auto Parts</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>Roshlin Auto Parts</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>9861537791</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 12:21:12 PM</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr"/>
+      <c r="T43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t>9861537791</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 12:21:12 PM</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 02:04:13 PM</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y43" s="3" t="inlineStr">
+        <is>
+          <t>27.722029</t>
+        </is>
+      </c>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA43" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB43" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC43" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD43" s="3" t="inlineStr"/>
+      <c r="AE43" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu 44600 Near by Valley Cold Store Pvt. Ltd., Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF43" s="3" t="inlineStr">
+        <is>
+          <t>sitaularaju570@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG43" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH43" s="3" t="inlineStr"/>
+      <c r="AI43" s="3" t="inlineStr">
+        <is>
+          <t>01:42 hour</t>
+        </is>
+      </c>
+      <c r="AJ43" s="3" t="inlineStr"/>
+      <c r="AK43" s="3" t="inlineStr"/>
+      <c r="AL43" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM43" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN43" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO43" s="3" t="inlineStr">
+        <is>
+          <t>2,3</t>
+        </is>
+      </c>
+      <c r="AP43" s="3" t="inlineStr">
+        <is>
+          <t>85.301869</t>
+        </is>
+      </c>
+      <c r="AQ43" s="3" t="inlineStr"/>
+      <c r="AR43" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
+        <is>
+          <t>1h 43m</t>
+        </is>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>1h 43m</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX43" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>5</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>68.2%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>15.9%</t>
         </is>
       </c>
     </row>
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>88.0%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>61.4%</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>5</v>
@@ -830,13 +830,13 @@
         <v>3</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>5</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>5</v>
@@ -970,13 +970,13 @@
         <v>7</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G7" s="4" t="n">
         <v>6</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -990,7 +990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX43"/>
+  <dimension ref="A1:AX45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -8194,10 +8194,8 @@
           <t>Shreyak Timsina</t>
         </is>
       </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t>9863626262</t>
-        </is>
+      <c r="O39" s="3" t="n">
+        <v>9863626262</v>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
@@ -8232,10 +8230,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y39" s="3" t="inlineStr">
-        <is>
-          <t>27.691212</t>
-        </is>
+      <c r="Y39" s="3" t="n">
+        <v>27.691212</v>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
@@ -8287,25 +8283,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN39" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN39" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
           <t>2,11</t>
         </is>
       </c>
-      <c r="AP39" s="3" t="inlineStr">
-        <is>
-          <t>85.323547</t>
-        </is>
+      <c r="AP39" s="3" t="n">
+        <v>85.323547</v>
       </c>
       <c r="AQ39" s="3" t="inlineStr"/>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6 upgrade  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
@@ -8514,10 +8506,8 @@
           <t>Manita Khadka</t>
         </is>
       </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>9842359754</t>
-        </is>
+      <c r="O41" s="3" t="n">
+        <v>9842359754</v>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
@@ -8607,10 +8597,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN41" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN41" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
@@ -8621,7 +8609,7 @@
       <c r="AQ41" s="3" t="inlineStr"/>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
@@ -8830,10 +8818,8 @@
           <t>Roshlin Auto Parts</t>
         </is>
       </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t>9861537791</t>
-        </is>
+      <c r="O43" s="3" t="n">
+        <v>9861537791</v>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
@@ -8868,10 +8854,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y43" s="3" t="inlineStr">
-        <is>
-          <t>27.722029</t>
-        </is>
+      <c r="Y43" s="3" t="n">
+        <v>27.722029</v>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
@@ -8927,55 +8911,479 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN43" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN43" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
           <t>2,3</t>
         </is>
       </c>
-      <c r="AP43" s="3" t="inlineStr">
-        <is>
-          <t>85.301869</t>
-        </is>
+      <c r="AP43" s="3" t="n">
+        <v>85.301869</v>
       </c>
       <c r="AQ43" s="3" t="inlineStr"/>
       <c r="AR43" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
+        <is>
+          <t>1h 43m</t>
+        </is>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>1h 43m</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS43" s="3" t="inlineStr">
-        <is>
-          <t>1h 43m</t>
-        </is>
-      </c>
-      <c r="AT43" s="3" t="inlineStr">
-        <is>
-          <t>1h 43m</t>
-        </is>
-      </c>
-      <c r="AU43" s="3" t="inlineStr">
+      <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX43" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 2:21 PM</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 Router</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351412</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>Jit Narayan Maharjan</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>Jit Narayan Maharjan</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t>9841403020</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:24:35 PM</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t>9818321365</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:24:35 PM</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 02:21:38 PM</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y44" s="3" t="inlineStr">
+        <is>
+          <t>27.709437</t>
+        </is>
+      </c>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA44" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB44" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC44" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD44" s="3" t="inlineStr"/>
+      <c r="AE44" s="3" t="inlineStr">
+        <is>
+          <t>Beside Durga Dairy and Bakery- Opp Bhelu Mahadev Temple, Dallu- 15, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF44" s="3" t="inlineStr">
+        <is>
+          <t>mytrek2nepal@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG44" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH44" s="3" t="inlineStr"/>
+      <c r="AI44" s="3" t="inlineStr">
+        <is>
+          <t>10:57 hour</t>
+        </is>
+      </c>
+      <c r="AJ44" s="3" t="inlineStr"/>
+      <c r="AK44" s="3" t="inlineStr"/>
+      <c r="AL44" s="3" t="inlineStr">
+        <is>
+          <t>Seeta Magar</t>
+        </is>
+      </c>
+      <c r="AM44" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN44" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO44" s="3" t="inlineStr">
+        <is>
+          <t>1,11</t>
+        </is>
+      </c>
+      <c r="AP44" s="3" t="inlineStr">
+        <is>
+          <t>85.301563</t>
+        </is>
+      </c>
+      <c r="AQ44" s="3" t="inlineStr"/>
+      <c r="AR44" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS44" s="3" t="inlineStr">
+        <is>
+          <t>1d 57m</t>
+        </is>
+      </c>
+      <c r="AT44" s="3" t="inlineStr">
+        <is>
+          <t>1d 57m</t>
+        </is>
+      </c>
+      <c r="AU44" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="AV43" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW43" s="3" t="inlineStr">
+      <c r="AV44" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW44" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX43" s="3" t="inlineStr">
-        <is>
-          <t>Sunil Chaudhary</t>
+      <c r="AX44" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 2:31 PM</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351122</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>Dipak Adhikari</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>Dipak Adhikari</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>9824661718</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr"/>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:32:46 AM</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr"/>
+      <c r="T45" s="3" t="inlineStr"/>
+      <c r="U45" s="3" t="inlineStr">
+        <is>
+          <t>9801137187</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:32:46 AM</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 02:31:00 PM</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y45" s="3" t="inlineStr">
+        <is>
+          <t>27.67667</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA45" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB45" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC45" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD45" s="3" t="inlineStr"/>
+      <c r="AE45" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur Patan Dhoka ward no:10 near Ashok party Palace, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF45" s="3" t="inlineStr">
+        <is>
+          <t>adhakaridipak@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG45" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH45" s="3" t="inlineStr"/>
+      <c r="AI45" s="3" t="inlineStr"/>
+      <c r="AJ45" s="3" t="inlineStr"/>
+      <c r="AK45" s="3" t="inlineStr"/>
+      <c r="AL45" s="3" t="inlineStr">
+        <is>
+          <t>Sabina K.C</t>
+        </is>
+      </c>
+      <c r="AM45" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN45" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO45" s="3" t="inlineStr">
+        <is>
+          <t>4,10</t>
+        </is>
+      </c>
+      <c r="AP45" s="3" t="inlineStr">
+        <is>
+          <t>85.3217</t>
+        </is>
+      </c>
+      <c r="AQ45" s="3" t="inlineStr"/>
+      <c r="AR45" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS45" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 58m</t>
+        </is>
+      </c>
+      <c r="AT45" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 58m</t>
+        </is>
+      </c>
+      <c r="AU45" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV45" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW45" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX45" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>6</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>67.3%</t>
         </is>
       </c>
     </row>
@@ -662,7 +662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -718,30 +718,53 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>16.3%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>2.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>85.2%</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>61.4%</t>
+      <c r="B4" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>61.2%</t>
         </is>
       </c>
     </row>
@@ -821,10 +844,10 @@
         <v>5</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>3</v>
@@ -833,20 +856,20 @@
         <v>6</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Specific Website/App is slow</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0</v>
@@ -855,7 +878,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>0</v>
@@ -870,7 +893,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Specific Website/App is slow</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -883,7 +906,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>0</v>
@@ -892,7 +915,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -958,13 +981,13 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>7</v>
@@ -973,10 +996,10 @@
         <v>6</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -990,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX45"/>
+  <dimension ref="A1:AX50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1030,7 +1053,7 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="19" customWidth="1" min="38" max="38"/>
+    <col width="22" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -9026,10 +9049,8 @@
           <t>Jit Narayan Maharjan</t>
         </is>
       </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t>9841403020</t>
-        </is>
+      <c r="O44" s="3" t="n">
+        <v>9841403020</v>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
@@ -9064,10 +9085,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y44" s="3" t="inlineStr">
-        <is>
-          <t>27.709437</t>
-        </is>
+      <c r="Y44" s="3" t="n">
+        <v>27.709437</v>
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
@@ -9123,25 +9142,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN44" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN44" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO44" s="3" t="inlineStr">
         <is>
           <t>1,11</t>
         </is>
       </c>
-      <c r="AP44" s="3" t="inlineStr">
-        <is>
-          <t>85.301563</t>
-        </is>
+      <c r="AP44" s="3" t="n">
+        <v>85.301563</v>
       </c>
       <c r="AQ44" s="3" t="inlineStr"/>
       <c r="AR44" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 Router   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS44" s="3" t="inlineStr">
@@ -9242,10 +9257,8 @@
           <t>Dipak Adhikari</t>
         </is>
       </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t>9824661718</t>
-        </is>
+      <c r="O45" s="3" t="n">
+        <v>9824661718</v>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
@@ -9280,10 +9293,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y45" s="3" t="inlineStr">
-        <is>
-          <t>27.67667</t>
-        </is>
+      <c r="Y45" s="3" t="n">
+        <v>27.67667</v>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
@@ -9335,55 +9346,1115 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN45" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN45" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
           <t>4,10</t>
         </is>
       </c>
-      <c r="AP45" s="3" t="inlineStr">
-        <is>
-          <t>85.3217</t>
-        </is>
+      <c r="AP45" s="3" t="n">
+        <v>85.32170000000001</v>
       </c>
       <c r="AQ45" s="3" t="inlineStr"/>
       <c r="AR45" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS45" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 58m</t>
+        </is>
+      </c>
+      <c r="AT45" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 58m</t>
+        </is>
+      </c>
+      <c r="AU45" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV45" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS45" s="3" t="inlineStr">
-        <is>
-          <t>1d 3h 58m</t>
-        </is>
-      </c>
-      <c r="AT45" s="3" t="inlineStr">
-        <is>
-          <t>1d 3h 58m</t>
-        </is>
-      </c>
-      <c r="AU45" s="3" t="inlineStr">
+      <c r="AW45" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX45" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 2:33 PM</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>IPTV ISSUE</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352510</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Barjachrya</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Barjachrya</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>9841255601</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr"/>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 12:28:07 PM</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="inlineStr"/>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t>CHB9841255601</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 12:05:06 PM</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 02:33:17 PM</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA46" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB46" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC46" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD46" s="3" t="inlineStr"/>
+      <c r="AE46" s="3" t="inlineStr">
+        <is>
+          <t>Lazimpat, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF46" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh@gamil.com</t>
+        </is>
+      </c>
+      <c r="AG46" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH46" s="3" t="inlineStr"/>
+      <c r="AI46" s="3" t="inlineStr"/>
+      <c r="AJ46" s="3" t="inlineStr"/>
+      <c r="AK46" s="3" t="inlineStr"/>
+      <c r="AL46" s="3" t="inlineStr">
+        <is>
+          <t>Bishwojeet Adhikari</t>
+        </is>
+      </c>
+      <c r="AM46" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN46" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO46" s="3" t="inlineStr">
+        <is>
+          <t>CDB328</t>
+        </is>
+      </c>
+      <c r="AP46" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ46" s="3" t="inlineStr"/>
+      <c r="AR46" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS46" s="3" t="inlineStr">
+        <is>
+          <t>2h 5m</t>
+        </is>
+      </c>
+      <c r="AT46" s="3" t="inlineStr">
+        <is>
+          <t>2h 28m</t>
+        </is>
+      </c>
+      <c r="AU46" s="3" t="inlineStr">
         <is>
           <t>Other / In Progress (On Hold)</t>
         </is>
       </c>
-      <c r="AV45" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW45" s="3" t="inlineStr">
+      <c r="AV46" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW46" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX46" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 2:39 PM</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352482</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>Subarna Raj Shrestha</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
+          <t>Subarna Raj Shrestha</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="inlineStr">
+        <is>
+          <t>9851062019</t>
+        </is>
+      </c>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q47" s="3" t="inlineStr"/>
+      <c r="R47" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 02:39:12 PM</t>
+        </is>
+      </c>
+      <c r="S47" s="3" t="inlineStr"/>
+      <c r="T47" s="3" t="inlineStr"/>
+      <c r="U47" s="3" t="inlineStr">
+        <is>
+          <t>9851062019</t>
+        </is>
+      </c>
+      <c r="V47" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 11:47:28 AM</t>
+        </is>
+      </c>
+      <c r="W47" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 02:39:12 PM</t>
+        </is>
+      </c>
+      <c r="X47" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y47" s="3" t="inlineStr"/>
+      <c r="Z47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA47" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB47" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC47" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD47" s="3" t="inlineStr"/>
+      <c r="AE47" s="3" t="inlineStr">
+        <is>
+          <t>Siddhartha Cottage - Love hotel Pulchowk - Dhobighat Rd Lalitpur 44700, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF47" s="3" t="inlineStr">
+        <is>
+          <t>subarna1414@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG47" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH47" s="3" t="inlineStr"/>
+      <c r="AI47" s="3" t="inlineStr">
+        <is>
+          <t>02:52 hour</t>
+        </is>
+      </c>
+      <c r="AJ47" s="3" t="inlineStr"/>
+      <c r="AK47" s="3" t="inlineStr"/>
+      <c r="AL47" s="3" t="inlineStr">
+        <is>
+          <t>Praktisha Subedi</t>
+        </is>
+      </c>
+      <c r="AM47" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN47" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO47" s="3" t="inlineStr">
+        <is>
+          <t>3,4</t>
+        </is>
+      </c>
+      <c r="AP47" s="3" t="inlineStr"/>
+      <c r="AQ47" s="3" t="inlineStr"/>
+      <c r="AR47" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS47" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT47" s="3" t="inlineStr">
+        <is>
+          <t>2h 51m</t>
+        </is>
+      </c>
+      <c r="AU47" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV47" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX47" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 2:45 PM</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>TKT1341380</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>Aama Milan Kendra</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>Aama Milan Kendra</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="inlineStr">
+        <is>
+          <t>9851220331</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q48" s="3" t="inlineStr"/>
+      <c r="R48" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:50:27 PM</t>
+        </is>
+      </c>
+      <c r="S48" s="3" t="inlineStr"/>
+      <c r="T48" s="3" t="inlineStr"/>
+      <c r="U48" s="3" t="inlineStr">
+        <is>
+          <t>9841863259</t>
+        </is>
+      </c>
+      <c r="V48" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 02:06:54 PM</t>
+        </is>
+      </c>
+      <c r="W48" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 02:45:10 PM</t>
+        </is>
+      </c>
+      <c r="X48" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y48" s="3" t="inlineStr">
+        <is>
+          <t>27.6907</t>
+        </is>
+      </c>
+      <c r="Z48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA48" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB48" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC48" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD48" s="3" t="inlineStr"/>
+      <c r="AE48" s="3" t="inlineStr">
+        <is>
+          <t>Chakrabarti Habi Education Academy College of Law,Bijulibazar, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF48" s="3" t="inlineStr">
+        <is>
+          <t>workcgnet@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG48" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH48" s="3" t="inlineStr"/>
+      <c r="AI48" s="3" t="inlineStr"/>
+      <c r="AJ48" s="3" t="inlineStr"/>
+      <c r="AK48" s="3" t="inlineStr"/>
+      <c r="AL48" s="3" t="inlineStr">
+        <is>
+          <t>Sabina K.C</t>
+        </is>
+      </c>
+      <c r="AM48" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN48" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO48" s="3" t="inlineStr">
+        <is>
+          <t>L48-6</t>
+        </is>
+      </c>
+      <c r="AP48" s="3" t="inlineStr">
+        <is>
+          <t>85.32893</t>
+        </is>
+      </c>
+      <c r="AQ48" s="3" t="inlineStr"/>
+      <c r="AR48" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>21h 54m</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>9d 38m</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV48" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW48" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX45" s="3" t="inlineStr">
-        <is>
-          <t>Shashikant Chaudhary</t>
+      <c r="AX48" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 2:38 PM</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352608</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>Bhoj Bahadur Bhujel</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>Bhoj Bahadur Bhujel</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>9845296408</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q49" s="3" t="inlineStr"/>
+      <c r="R49" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 02:38:26 PM</t>
+        </is>
+      </c>
+      <c r="S49" s="3" t="inlineStr"/>
+      <c r="T49" s="3" t="inlineStr"/>
+      <c r="U49" s="3" t="inlineStr">
+        <is>
+          <t>9845296408</t>
+        </is>
+      </c>
+      <c r="V49" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 01:11:10 PM</t>
+        </is>
+      </c>
+      <c r="W49" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 02:38:26 PM</t>
+        </is>
+      </c>
+      <c r="X49" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y49" s="3" t="inlineStr">
+        <is>
+          <t>27.69751</t>
+        </is>
+      </c>
+      <c r="Z49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA49" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB49" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC49" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD49" s="3" t="inlineStr"/>
+      <c r="AE49" s="3" t="inlineStr">
+        <is>
+          <t>Sinamangal-9,near Tara Hall Chowk, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF49" s="3" t="inlineStr"/>
+      <c r="AG49" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH49" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI49" s="3" t="inlineStr">
+        <is>
+          <t>01:27 hour</t>
+        </is>
+      </c>
+      <c r="AJ49" s="3" t="inlineStr"/>
+      <c r="AK49" s="3" t="inlineStr"/>
+      <c r="AL49" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM49" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN49" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO49" s="3" t="inlineStr">
+        <is>
+          <t>L58-1</t>
+        </is>
+      </c>
+      <c r="AP49" s="3" t="inlineStr">
+        <is>
+          <t>85.35184</t>
+        </is>
+      </c>
+      <c r="AQ49" s="3" t="inlineStr"/>
+      <c r="AR49" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS49" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT49" s="3" t="inlineStr">
+        <is>
+          <t>1h 27m</t>
+        </is>
+      </c>
+      <c r="AU49" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV49" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW49" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX49" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 2:47 PM</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr"/>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352480</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>Roshan bohara</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>Roshan bohara</t>
+        </is>
+      </c>
+      <c r="O50" s="3" t="inlineStr">
+        <is>
+          <t>9810253862</t>
+        </is>
+      </c>
+      <c r="P50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q50" s="3" t="inlineStr"/>
+      <c r="R50" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 11:47:01 AM</t>
+        </is>
+      </c>
+      <c r="S50" s="3" t="inlineStr"/>
+      <c r="T50" s="3" t="inlineStr"/>
+      <c r="U50" s="3" t="inlineStr">
+        <is>
+          <t>9860459683</t>
+        </is>
+      </c>
+      <c r="V50" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 11:47:01 AM</t>
+        </is>
+      </c>
+      <c r="W50" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 02:47:20 PM</t>
+        </is>
+      </c>
+      <c r="X50" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y50" s="3" t="inlineStr">
+        <is>
+          <t>27.73369</t>
+        </is>
+      </c>
+      <c r="Z50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA50" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB50" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC50" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD50" s="3" t="inlineStr"/>
+      <c r="AE50" s="3" t="inlineStr">
+        <is>
+          <t>Balaju Prithivi durbar, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF50" s="3" t="inlineStr">
+        <is>
+          <t>roshanbohara89@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG50" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH50" s="3" t="inlineStr"/>
+      <c r="AI50" s="3" t="inlineStr">
+        <is>
+          <t>03:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ50" s="3" t="inlineStr"/>
+      <c r="AK50" s="3" t="inlineStr"/>
+      <c r="AL50" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM50" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN50" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO50" s="3" t="inlineStr">
+        <is>
+          <t>2,15</t>
+        </is>
+      </c>
+      <c r="AP50" s="3" t="inlineStr">
+        <is>
+          <t>85.29389</t>
+        </is>
+      </c>
+      <c r="AQ50" s="3" t="inlineStr"/>
+      <c r="AR50" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS50" s="3" t="inlineStr">
+        <is>
+          <t>3h</t>
+        </is>
+      </c>
+      <c r="AT50" s="3" t="inlineStr">
+        <is>
+          <t>3h</t>
+        </is>
+      </c>
+      <c r="AU50" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV50" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW50" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX50" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
@@ -1059,7 +1059,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -9451,20 +9451,14 @@
           <t>On Hold</t>
         </is>
       </c>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M46" s="3" t="inlineStr"/>
       <c r="N46" s="3" t="inlineStr">
         <is>
           <t>Rajesh Barjachrya</t>
         </is>
       </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t>9841255601</t>
-        </is>
+      <c r="O46" s="3" t="n">
+        <v>9841255601</v>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
@@ -9499,10 +9493,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y46" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
@@ -9554,25 +9546,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN46" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN46" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO46" s="3" t="inlineStr">
         <is>
           <t>CDB328</t>
         </is>
       </c>
-      <c r="AP46" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP46" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ46" s="3" t="inlineStr"/>
       <c r="AR46" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV ISSUE  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS46" s="3" t="inlineStr">
@@ -9673,10 +9661,8 @@
           <t>Subarna Raj Shrestha</t>
         </is>
       </c>
-      <c r="O47" s="3" t="inlineStr">
-        <is>
-          <t>9851062019</t>
-        </is>
+      <c r="O47" s="3" t="n">
+        <v>9851062019</v>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
@@ -9766,10 +9752,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN47" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN47" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO47" s="3" t="inlineStr">
         <is>
@@ -9780,7 +9764,7 @@
       <c r="AQ47" s="3" t="inlineStr"/>
       <c r="AR47" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS47" s="3" t="inlineStr">
@@ -9881,10 +9865,8 @@
           <t>Aama Milan Kendra</t>
         </is>
       </c>
-      <c r="O48" s="3" t="inlineStr">
-        <is>
-          <t>9851220331</t>
-        </is>
+      <c r="O48" s="3" t="n">
+        <v>9851220331</v>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
@@ -9919,10 +9901,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y48" s="3" t="inlineStr">
-        <is>
-          <t>27.6907</t>
-        </is>
+      <c r="Y48" s="3" t="n">
+        <v>27.6907</v>
       </c>
       <c r="Z48" s="3" t="inlineStr">
         <is>
@@ -9974,25 +9954,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN48" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN48" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO48" s="3" t="inlineStr">
         <is>
           <t>L48-6</t>
         </is>
       </c>
-      <c r="AP48" s="3" t="inlineStr">
-        <is>
-          <t>85.32893</t>
-        </is>
+      <c r="AP48" s="3" t="n">
+        <v>85.32893</v>
       </c>
       <c r="AQ48" s="3" t="inlineStr"/>
       <c r="AR48" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS48" s="3" t="inlineStr">
@@ -10093,10 +10069,8 @@
           <t>Bhoj Bahadur Bhujel</t>
         </is>
       </c>
-      <c r="O49" s="3" t="inlineStr">
-        <is>
-          <t>9845296408</t>
-        </is>
+      <c r="O49" s="3" t="n">
+        <v>9845296408</v>
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
@@ -10131,10 +10105,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y49" s="3" t="inlineStr">
-        <is>
-          <t>27.69751</t>
-        </is>
+      <c r="Y49" s="3" t="n">
+        <v>27.69751</v>
       </c>
       <c r="Z49" s="3" t="inlineStr">
         <is>
@@ -10168,10 +10140,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH49" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH49" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI49" s="3" t="inlineStr">
         <is>
@@ -10190,25 +10160,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN49" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN49" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO49" s="3" t="inlineStr">
         <is>
           <t>L58-1</t>
         </is>
       </c>
-      <c r="AP49" s="3" t="inlineStr">
-        <is>
-          <t>85.35184</t>
-        </is>
+      <c r="AP49" s="3" t="n">
+        <v>85.35184</v>
       </c>
       <c r="AQ49" s="3" t="inlineStr"/>
       <c r="AR49" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS49" s="3" t="inlineStr">
@@ -10309,10 +10275,8 @@
           <t>Roshan bohara</t>
         </is>
       </c>
-      <c r="O50" s="3" t="inlineStr">
-        <is>
-          <t>9810253862</t>
-        </is>
+      <c r="O50" s="3" t="n">
+        <v>9810253862</v>
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
@@ -10347,10 +10311,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y50" s="3" t="inlineStr">
-        <is>
-          <t>27.73369</t>
-        </is>
+      <c r="Y50" s="3" t="n">
+        <v>27.73369</v>
       </c>
       <c r="Z50" s="3" t="inlineStr">
         <is>
@@ -10406,25 +10368,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN50" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN50" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO50" s="3" t="inlineStr">
         <is>
           <t>2,15</t>
         </is>
       </c>
-      <c r="AP50" s="3" t="inlineStr">
-        <is>
-          <t>85.29389</t>
-        </is>
+      <c r="AP50" s="3" t="n">
+        <v>85.29389</v>
       </c>
       <c r="AQ50" s="3" t="inlineStr"/>
       <c r="AR50" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS50" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>6</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>33</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>66.0%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>16.0%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>25</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>80.6%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>62.0%</t>
         </is>
       </c>
     </row>
@@ -856,10 +856,10 @@
         <v>6</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3">
@@ -996,10 +996,10 @@
         <v>6</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1013,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX50"/>
+  <dimension ref="A1:AX51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1027,7 +1027,7 @@
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="34" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="34" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
@@ -1059,7 +1059,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -10416,6 +10416,214 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 3:25 PM</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr"/>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352004</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>Ram Lakhan Sharma</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
+          <t>Ram Lakhan Sharma</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>9851153192</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q51" s="3" t="inlineStr"/>
+      <c r="R51" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 08:44:43 PM</t>
+        </is>
+      </c>
+      <c r="S51" s="3" t="inlineStr"/>
+      <c r="T51" s="3" t="inlineStr"/>
+      <c r="U51" s="3" t="inlineStr">
+        <is>
+          <t>9851153192</t>
+        </is>
+      </c>
+      <c r="V51" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 08:44:43 PM</t>
+        </is>
+      </c>
+      <c r="W51" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 03:25:02 PM</t>
+        </is>
+      </c>
+      <c r="X51" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y51" s="3" t="inlineStr">
+        <is>
+          <t>27.70276</t>
+        </is>
+      </c>
+      <c r="Z51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA51" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB51" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC51" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD51" s="3" t="inlineStr"/>
+      <c r="AE51" s="3" t="inlineStr">
+        <is>
+          <t>Syuchatar Pati Chowk,Syuchatar, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF51" s="3" t="inlineStr"/>
+      <c r="AG51" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH51" s="3" t="inlineStr"/>
+      <c r="AI51" s="3" t="inlineStr"/>
+      <c r="AJ51" s="3" t="inlineStr"/>
+      <c r="AK51" s="3" t="inlineStr"/>
+      <c r="AL51" s="3" t="inlineStr">
+        <is>
+          <t>Ishlok Shahi</t>
+        </is>
+      </c>
+      <c r="AM51" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN51" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO51" s="3" t="inlineStr">
+        <is>
+          <t>CDB201</t>
+        </is>
+      </c>
+      <c r="AP51" s="3" t="inlineStr">
+        <is>
+          <t>85.27484</t>
+        </is>
+      </c>
+      <c r="AQ51" s="3" t="inlineStr"/>
+      <c r="AR51" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS51" s="3" t="inlineStr">
+        <is>
+          <t>18h 40m</t>
+        </is>
+      </c>
+      <c r="AT51" s="3" t="inlineStr">
+        <is>
+          <t>18h 40m</t>
+        </is>
+      </c>
+      <c r="AU51" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV51" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW51" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX51" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>5</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>68.4%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>19.3%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>1.8%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>82.9%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>61.4%</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -844,10 +844,10 @@
         <v>5</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>3</v>
@@ -859,17 +859,17 @@
         <v>7</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Specific Website/App is slow</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0</v>
@@ -878,7 +878,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>0</v>
@@ -887,17 +887,17 @@
         <v>0</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Specific Website/App is slow</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
@@ -906,7 +906,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>0</v>
@@ -921,7 +921,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Payment Inquiry</t>
+          <t>Due to Configuration Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -931,10 +931,10 @@
         <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>Payment Inquiry</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -962,44 +962,72 @@
         <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Other / Uncategorized</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B8" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C8" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="D7" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G7" s="4" t="n">
+      <c r="G8" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="H7" s="4" t="n">
-        <v>39</v>
+      <c r="H8" s="4" t="n">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1013,7 +1041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX51"/>
+  <dimension ref="A1:AX58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1026,12 +1054,12 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="34" customWidth="1" min="14" max="14"/>
+    <col width="45" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="32" customWidth="1" min="16" max="16"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
@@ -1041,13 +1069,13 @@
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="32" customWidth="1" min="26" max="26"/>
+    <col width="34" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="21" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="31" customWidth="1" min="32" max="32"/>
+    <col width="33" customWidth="1" min="32" max="32"/>
     <col width="31" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -10473,20 +10501,14 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="M51" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M51" s="3" t="inlineStr"/>
       <c r="N51" s="3" t="inlineStr">
         <is>
           <t>Ram Lakhan Sharma</t>
         </is>
       </c>
-      <c r="O51" s="3" t="inlineStr">
-        <is>
-          <t>9851153192</t>
-        </is>
+      <c r="O51" s="3" t="n">
+        <v>9851153192</v>
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
@@ -10521,10 +10543,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y51" s="3" t="inlineStr">
-        <is>
-          <t>27.70276</t>
-        </is>
+      <c r="Y51" s="3" t="n">
+        <v>27.70276</v>
       </c>
       <c r="Z51" s="3" t="inlineStr">
         <is>
@@ -10572,55 +10592,1531 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN51" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN51" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO51" s="3" t="inlineStr">
         <is>
           <t>CDB201</t>
         </is>
       </c>
-      <c r="AP51" s="3" t="inlineStr">
-        <is>
-          <t>85.27484</t>
-        </is>
+      <c r="AP51" s="3" t="n">
+        <v>85.27484</v>
       </c>
       <c r="AQ51" s="3" t="inlineStr"/>
       <c r="AR51" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS51" s="3" t="inlineStr">
+        <is>
+          <t>18h 40m</t>
+        </is>
+      </c>
+      <c r="AT51" s="3" t="inlineStr">
+        <is>
+          <t>18h 40m</t>
+        </is>
+      </c>
+      <c r="AU51" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV51" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS51" s="3" t="inlineStr">
-        <is>
-          <t>18h 40m</t>
-        </is>
-      </c>
-      <c r="AT51" s="3" t="inlineStr">
-        <is>
-          <t>18h 40m</t>
-        </is>
-      </c>
-      <c r="AU51" s="3" t="inlineStr">
+      <c r="AW51" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX51" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 3:22 PM</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr"/>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351122</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>Dipak Adhikari</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
+          <t>Dipak Adhikari</t>
+        </is>
+      </c>
+      <c r="O52" s="3" t="inlineStr">
+        <is>
+          <t>9824661718</t>
+        </is>
+      </c>
+      <c r="P52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q52" s="3" t="inlineStr"/>
+      <c r="R52" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 03:22:25 PM</t>
+        </is>
+      </c>
+      <c r="S52" s="3" t="inlineStr"/>
+      <c r="T52" s="3" t="inlineStr"/>
+      <c r="U52" s="3" t="inlineStr">
+        <is>
+          <t>9801137187</t>
+        </is>
+      </c>
+      <c r="V52" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:32:46 AM</t>
+        </is>
+      </c>
+      <c r="W52" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 03:22:25 PM</t>
+        </is>
+      </c>
+      <c r="X52" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y52" s="3" t="inlineStr">
+        <is>
+          <t>27.67667</t>
+        </is>
+      </c>
+      <c r="Z52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA52" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB52" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC52" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD52" s="3" t="inlineStr"/>
+      <c r="AE52" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur Patan Dhoka ward no:10 near Ashok party Palace, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF52" s="3" t="inlineStr">
+        <is>
+          <t>adhakaridipak@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG52" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH52" s="3" t="inlineStr"/>
+      <c r="AI52" s="3" t="inlineStr">
+        <is>
+          <t>14:50 hour</t>
+        </is>
+      </c>
+      <c r="AJ52" s="3" t="inlineStr"/>
+      <c r="AK52" s="3" t="inlineStr"/>
+      <c r="AL52" s="3" t="inlineStr">
+        <is>
+          <t>Sabina K.C</t>
+        </is>
+      </c>
+      <c r="AM52" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN52" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO52" s="3" t="inlineStr">
+        <is>
+          <t>4,10</t>
+        </is>
+      </c>
+      <c r="AP52" s="3" t="inlineStr">
+        <is>
+          <t>85.3217</t>
+        </is>
+      </c>
+      <c r="AQ52" s="3" t="inlineStr"/>
+      <c r="AR52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS52" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT52" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 49m</t>
+        </is>
+      </c>
+      <c r="AU52" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW52" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX52" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 3:25 PM</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr"/>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6 Router Upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>wifi6 Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352536</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>Mary Ward School</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
+          <t>Mary Ward School</t>
+        </is>
+      </c>
+      <c r="O53" s="3" t="inlineStr">
+        <is>
+          <t>9849554115</t>
+        </is>
+      </c>
+      <c r="P53" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q53" s="3" t="inlineStr"/>
+      <c r="R53" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 03:25:39 PM</t>
+        </is>
+      </c>
+      <c r="S53" s="3" t="inlineStr"/>
+      <c r="T53" s="3" t="inlineStr"/>
+      <c r="U53" s="3" t="inlineStr">
+        <is>
+          <t>LTP9849554115</t>
+        </is>
+      </c>
+      <c r="V53" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 12:20:13 PM</t>
+        </is>
+      </c>
+      <c r="W53" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 03:25:39 PM</t>
+        </is>
+      </c>
+      <c r="X53" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y53" s="3" t="inlineStr"/>
+      <c r="Z53" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA53" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB53" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC53" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD53" s="3" t="inlineStr"/>
+      <c r="AE53" s="3" t="inlineStr">
+        <is>
+          <t>Arun Thapa Statue - Sculpture ???? ???? ??? 44700, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF53" s="3" t="inlineStr">
+        <is>
+          <t>9849554115@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG53" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH53" s="3" t="inlineStr"/>
+      <c r="AI53" s="3" t="inlineStr">
+        <is>
+          <t>03:05 hour</t>
+        </is>
+      </c>
+      <c r="AJ53" s="3" t="inlineStr"/>
+      <c r="AK53" s="3" t="inlineStr"/>
+      <c r="AL53" s="3" t="inlineStr">
+        <is>
+          <t>Aashna Pulami</t>
+        </is>
+      </c>
+      <c r="AM53" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN53" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO53" s="3" t="inlineStr">
+        <is>
+          <t>3,8</t>
+        </is>
+      </c>
+      <c r="AP53" s="3" t="inlineStr"/>
+      <c r="AQ53" s="3" t="inlineStr"/>
+      <c r="AR53" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6 Router Upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS53" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT53" s="3" t="inlineStr">
+        <is>
+          <t>3h 5m</t>
+        </is>
+      </c>
+      <c r="AU53" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV53" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6 Router Upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW53" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX53" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 3:15 PM</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr"/>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Case : interent not working  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>interent not working</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>TKT1342441</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>Dex Nine pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
+          <t>Dex Nine pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="O54" s="3" t="inlineStr">
+        <is>
+          <t>9865995180</t>
+        </is>
+      </c>
+      <c r="P54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q54" s="3" t="inlineStr"/>
+      <c r="R54" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 09:27:35 AM</t>
+        </is>
+      </c>
+      <c r="S54" s="3" t="inlineStr"/>
+      <c r="T54" s="3" t="inlineStr"/>
+      <c r="U54" s="3" t="inlineStr">
+        <is>
+          <t>LTP9700022257</t>
+        </is>
+      </c>
+      <c r="V54" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 01:33:16 PM</t>
+        </is>
+      </c>
+      <c r="W54" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 03:15:31 PM</t>
+        </is>
+      </c>
+      <c r="X54" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y54" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA54" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB54" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC54" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD54" s="3" t="inlineStr">
+        <is>
+          <t>Request</t>
+        </is>
+      </c>
+      <c r="AE54" s="3" t="inlineStr">
+        <is>
+          <t>27.646537000000006, 85.31367780674677, Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF54" s="3" t="inlineStr">
+        <is>
+          <t>dexnineco@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG54" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH54" s="3" t="inlineStr"/>
+      <c r="AI54" s="3" t="inlineStr"/>
+      <c r="AJ54" s="3" t="inlineStr"/>
+      <c r="AK54" s="3" t="inlineStr"/>
+      <c r="AL54" s="3" t="inlineStr"/>
+      <c r="AM54" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN54" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO54" s="3" t="inlineStr">
+        <is>
+          <t>CDB517</t>
+        </is>
+      </c>
+      <c r="AP54" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ54" s="3" t="inlineStr"/>
+      <c r="AR54" s="3" t="inlineStr">
+        <is>
+          <t>Case : interent not working  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS54" s="3" t="inlineStr">
+        <is>
+          <t>5h 47m</t>
+        </is>
+      </c>
+      <c r="AT54" s="3" t="inlineStr">
+        <is>
+          <t>8d 1h 42m</t>
+        </is>
+      </c>
+      <c r="AU54" s="3" t="inlineStr">
         <is>
           <t>Other / In Progress (In Progress)</t>
         </is>
       </c>
-      <c r="AV51" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW51" s="3" t="inlineStr">
+      <c r="AV54" s="3" t="inlineStr">
+        <is>
+          <t>Case : interent not working  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX54" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 2:58 PM</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr"/>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>slow internet</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>TKT1349961</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>Global Dreams Educational Consultancy Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
+          <t>Global Dreams Educational Consultancy Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
+          <t>9801220336</t>
+        </is>
+      </c>
+      <c r="P55" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q55" s="3" t="inlineStr"/>
+      <c r="R55" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 02:58:56 PM</t>
+        </is>
+      </c>
+      <c r="S55" s="3" t="inlineStr"/>
+      <c r="T55" s="3" t="inlineStr"/>
+      <c r="U55" s="3" t="inlineStr">
+        <is>
+          <t>9801220336</t>
+        </is>
+      </c>
+      <c r="V55" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 01:23:35 PM</t>
+        </is>
+      </c>
+      <c r="W55" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 02:58:56 PM</t>
+        </is>
+      </c>
+      <c r="X55" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y55" s="3" t="inlineStr"/>
+      <c r="Z55" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA55" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB55" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC55" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD55" s="3" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="AE55" s="3" t="inlineStr">
+        <is>
+          <t>Putalisadak area	, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF55" s="3" t="inlineStr">
+        <is>
+          <t>srjstha86@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG55" s="3" t="inlineStr">
+        <is>
+          <t>Specific Website/App is slow</t>
+        </is>
+      </c>
+      <c r="AH55" s="3" t="inlineStr"/>
+      <c r="AI55" s="3" t="inlineStr">
+        <is>
+          <t>21:35 hour</t>
+        </is>
+      </c>
+      <c r="AJ55" s="3" t="inlineStr"/>
+      <c r="AK55" s="3" t="inlineStr"/>
+      <c r="AL55" s="3" t="inlineStr"/>
+      <c r="AM55" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN55" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO55" s="3" t="inlineStr">
+        <is>
+          <t>4,10</t>
+        </is>
+      </c>
+      <c r="AP55" s="3" t="inlineStr"/>
+      <c r="AQ55" s="3" t="inlineStr"/>
+      <c r="AR55" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS55" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT55" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 35m</t>
+        </is>
+      </c>
+      <c r="AU55" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV55" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW55" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX55" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 3:31 PM</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr"/>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>For upgradation to wifi6</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351957</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>Biswash Dhakal</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
+          <t>Biswash Dhakal</t>
+        </is>
+      </c>
+      <c r="O56" s="3" t="inlineStr">
+        <is>
+          <t>9841538079</t>
+        </is>
+      </c>
+      <c r="P56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q56" s="3" t="inlineStr"/>
+      <c r="R56" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 03:31:57 PM</t>
+        </is>
+      </c>
+      <c r="S56" s="3" t="inlineStr"/>
+      <c r="T56" s="3" t="inlineStr"/>
+      <c r="U56" s="3" t="inlineStr">
+        <is>
+          <t>9802326413</t>
+        </is>
+      </c>
+      <c r="V56" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 07:58:34 PM</t>
+        </is>
+      </c>
+      <c r="W56" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 03:31:57 PM</t>
+        </is>
+      </c>
+      <c r="X56" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y56" s="3" t="inlineStr">
+        <is>
+          <t>27.67592</t>
+        </is>
+      </c>
+      <c r="Z56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA56" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB56" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC56" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD56" s="3" t="inlineStr"/>
+      <c r="AE56" s="3" t="inlineStr">
+        <is>
+          <t>Reload fashion wear - Clothing store M9H3+JFC Kathmandu 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF56" s="3" t="inlineStr">
+        <is>
+          <t>danzerbunker123@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG56" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH56" s="3" t="inlineStr"/>
+      <c r="AI56" s="3" t="inlineStr">
+        <is>
+          <t>05:33 hour</t>
+        </is>
+      </c>
+      <c r="AJ56" s="3" t="inlineStr"/>
+      <c r="AK56" s="3" t="inlineStr"/>
+      <c r="AL56" s="3" t="inlineStr">
+        <is>
+          <t>Pradeep Yadav</t>
+        </is>
+      </c>
+      <c r="AM56" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN56" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO56" s="3" t="inlineStr">
+        <is>
+          <t>L7-8</t>
+        </is>
+      </c>
+      <c r="AP56" s="3" t="inlineStr">
+        <is>
+          <t>85.34561</t>
+        </is>
+      </c>
+      <c r="AQ56" s="3" t="inlineStr"/>
+      <c r="AR56" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS56" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT56" s="3" t="inlineStr">
+        <is>
+          <t>19h 33m</t>
+        </is>
+      </c>
+      <c r="AU56" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV56" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW56" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX51" s="3" t="inlineStr">
-        <is>
-          <t>Sunil Chaudhary</t>
+      <c r="AX56" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 3:30 PM</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr"/>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>Case : Frequent disconnection   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>Frequent disconnection</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352350</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>Rohit kumar</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
+          <t>Rohit kumar</t>
+        </is>
+      </c>
+      <c r="O57" s="3" t="inlineStr">
+        <is>
+          <t>9849109425</t>
+        </is>
+      </c>
+      <c r="P57" s="3" t="inlineStr">
+        <is>
+          <t>Frequent Internet Disconnection</t>
+        </is>
+      </c>
+      <c r="Q57" s="3" t="inlineStr"/>
+      <c r="R57" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 03:30:45 PM</t>
+        </is>
+      </c>
+      <c r="S57" s="3" t="inlineStr"/>
+      <c r="T57" s="3" t="inlineStr"/>
+      <c r="U57" s="3" t="inlineStr">
+        <is>
+          <t>9849109425</t>
+        </is>
+      </c>
+      <c r="V57" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 10:34:29 AM</t>
+        </is>
+      </c>
+      <c r="W57" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 03:30:45 PM</t>
+        </is>
+      </c>
+      <c r="X57" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y57" s="3" t="inlineStr"/>
+      <c r="Z57" s="3" t="inlineStr">
+        <is>
+          <t>Frequent Internet Disconnection</t>
+        </is>
+      </c>
+      <c r="AA57" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB57" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC57" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD57" s="3" t="inlineStr"/>
+      <c r="AE57" s="3" t="inlineStr">
+        <is>
+          <t>27.713837, 85.349362, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF57" s="3" t="inlineStr"/>
+      <c r="AG57" s="3" t="inlineStr">
+        <is>
+          <t>Due to Configuration Issue</t>
+        </is>
+      </c>
+      <c r="AH57" s="3" t="inlineStr"/>
+      <c r="AI57" s="3" t="inlineStr">
+        <is>
+          <t>04:56 hour</t>
+        </is>
+      </c>
+      <c r="AJ57" s="3" t="inlineStr"/>
+      <c r="AK57" s="3" t="inlineStr"/>
+      <c r="AL57" s="3" t="inlineStr">
+        <is>
+          <t>Prajwal Adhikari</t>
+        </is>
+      </c>
+      <c r="AM57" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN57" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO57" s="3" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="AP57" s="3" t="inlineStr"/>
+      <c r="AQ57" s="3" t="inlineStr"/>
+      <c r="AR57" s="3" t="inlineStr">
+        <is>
+          <t>Case : Frequent disconnection   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS57" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT57" s="3" t="inlineStr">
+        <is>
+          <t>4h 56m</t>
+        </is>
+      </c>
+      <c r="AU57" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV57" s="3" t="inlineStr">
+        <is>
+          <t>Case : Frequent disconnection   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW57" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX57" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 3:04 PM</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr"/>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352381</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>Ekta Jagodia</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>Follow Up</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
+          <t>Ekta Jagodia</t>
+        </is>
+      </c>
+      <c r="O58" s="3" t="inlineStr">
+        <is>
+          <t>9802075001</t>
+        </is>
+      </c>
+      <c r="P58" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q58" s="3" t="inlineStr"/>
+      <c r="R58" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 03:04:00 PM</t>
+        </is>
+      </c>
+      <c r="S58" s="3" t="inlineStr"/>
+      <c r="T58" s="3" t="inlineStr"/>
+      <c r="U58" s="3" t="inlineStr">
+        <is>
+          <t>9801059000</t>
+        </is>
+      </c>
+      <c r="V58" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 10:49:59 AM</t>
+        </is>
+      </c>
+      <c r="W58" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 03:04:00 PM</t>
+        </is>
+      </c>
+      <c r="X58" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y58" s="3" t="inlineStr">
+        <is>
+          <t>27.70343</t>
+        </is>
+      </c>
+      <c r="Z58" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA58" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB58" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC58" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD58" s="3" t="inlineStr"/>
+      <c r="AE58" s="3" t="inlineStr">
+        <is>
+          <t>In Rukmani Group, Maitidevi, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF58" s="3" t="inlineStr">
+        <is>
+          <t>administrator@rukmanigroup.com</t>
+        </is>
+      </c>
+      <c r="AG58" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH58" s="3" t="inlineStr"/>
+      <c r="AI58" s="3" t="inlineStr">
+        <is>
+          <t>04:15 hour</t>
+        </is>
+      </c>
+      <c r="AJ58" s="3" t="inlineStr"/>
+      <c r="AK58" s="3" t="inlineStr"/>
+      <c r="AL58" s="3" t="inlineStr">
+        <is>
+          <t>Kusum Gurung</t>
+        </is>
+      </c>
+      <c r="AM58" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN58" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO58" s="3" t="inlineStr">
+        <is>
+          <t>CDB052</t>
+        </is>
+      </c>
+      <c r="AP58" s="3" t="inlineStr">
+        <is>
+          <t>85.3345</t>
+        </is>
+      </c>
+      <c r="AQ58" s="3" t="inlineStr"/>
+      <c r="AR58" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS58" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT58" s="3" t="inlineStr">
+        <is>
+          <t>4h 14m</t>
+        </is>
+      </c>
+      <c r="AU58" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV58" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW58" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX58" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>81.8%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>6</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>72.7%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>69.4%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>10</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>19.4%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>1.6%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>82.9%</t>
+          <t>82.1%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>62.9%</t>
         </is>
       </c>
     </row>
@@ -841,25 +841,25 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>8</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>3</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>7</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
@@ -1009,25 +1009,25 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>8</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>8</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>8</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1041,7 +1041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX58"/>
+  <dimension ref="A1:AX63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -10707,10 +10707,8 @@
           <t>Dipak Adhikari</t>
         </is>
       </c>
-      <c r="O52" s="3" t="inlineStr">
-        <is>
-          <t>9824661718</t>
-        </is>
+      <c r="O52" s="3" t="n">
+        <v>9824661718</v>
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
@@ -10745,10 +10743,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y52" s="3" t="inlineStr">
-        <is>
-          <t>27.67667</t>
-        </is>
+      <c r="Y52" s="3" t="n">
+        <v>27.67667</v>
       </c>
       <c r="Z52" s="3" t="inlineStr">
         <is>
@@ -10804,25 +10800,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN52" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN52" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO52" s="3" t="inlineStr">
         <is>
           <t>4,10</t>
         </is>
       </c>
-      <c r="AP52" s="3" t="inlineStr">
-        <is>
-          <t>85.3217</t>
-        </is>
+      <c r="AP52" s="3" t="n">
+        <v>85.32170000000001</v>
       </c>
       <c r="AQ52" s="3" t="inlineStr"/>
       <c r="AR52" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS52" s="3" t="inlineStr">
@@ -10923,10 +10915,8 @@
           <t>Mary Ward School</t>
         </is>
       </c>
-      <c r="O53" s="3" t="inlineStr">
-        <is>
-          <t>9849554115</t>
-        </is>
+      <c r="O53" s="3" t="n">
+        <v>9849554115</v>
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
@@ -11016,10 +11006,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN53" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN53" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO53" s="3" t="inlineStr">
         <is>
@@ -11030,7 +11018,7 @@
       <c r="AQ53" s="3" t="inlineStr"/>
       <c r="AR53" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6 Router Upgrade   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS53" s="3" t="inlineStr">
@@ -11131,10 +11119,8 @@
           <t>Dex Nine pvt. Ltd.</t>
         </is>
       </c>
-      <c r="O54" s="3" t="inlineStr">
-        <is>
-          <t>9865995180</t>
-        </is>
+      <c r="O54" s="3" t="n">
+        <v>9865995180</v>
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
@@ -11169,10 +11155,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y54" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y54" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z54" s="3" t="inlineStr">
         <is>
@@ -11224,25 +11208,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN54" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN54" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO54" s="3" t="inlineStr">
         <is>
           <t>CDB517</t>
         </is>
       </c>
-      <c r="AP54" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP54" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ54" s="3" t="inlineStr"/>
       <c r="AR54" s="3" t="inlineStr">
         <is>
-          <t>Case : interent not working  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS54" s="3" t="inlineStr">
@@ -11343,10 +11323,8 @@
           <t>Global Dreams Educational Consultancy Pvt Ltd</t>
         </is>
       </c>
-      <c r="O55" s="3" t="inlineStr">
-        <is>
-          <t>9801220336</t>
-        </is>
+      <c r="O55" s="3" t="n">
+        <v>9801220336</v>
       </c>
       <c r="P55" s="3" t="inlineStr">
         <is>
@@ -11436,10 +11414,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN55" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN55" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO55" s="3" t="inlineStr">
         <is>
@@ -11450,7 +11426,7 @@
       <c r="AQ55" s="3" t="inlineStr"/>
       <c r="AR55" s="3" t="inlineStr">
         <is>
-          <t>Case : slow internet   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS55" s="3" t="inlineStr">
@@ -11551,10 +11527,8 @@
           <t>Biswash Dhakal</t>
         </is>
       </c>
-      <c r="O56" s="3" t="inlineStr">
-        <is>
-          <t>9841538079</t>
-        </is>
+      <c r="O56" s="3" t="n">
+        <v>9841538079</v>
       </c>
       <c r="P56" s="3" t="inlineStr">
         <is>
@@ -11589,10 +11563,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y56" s="3" t="inlineStr">
-        <is>
-          <t>27.67592</t>
-        </is>
+      <c r="Y56" s="3" t="n">
+        <v>27.67592</v>
       </c>
       <c r="Z56" s="3" t="inlineStr">
         <is>
@@ -11648,25 +11620,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN56" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN56" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO56" s="3" t="inlineStr">
         <is>
           <t>L7-8</t>
         </is>
       </c>
-      <c r="AP56" s="3" t="inlineStr">
-        <is>
-          <t>85.34561</t>
-        </is>
+      <c r="AP56" s="3" t="n">
+        <v>85.34560999999999</v>
       </c>
       <c r="AQ56" s="3" t="inlineStr"/>
       <c r="AR56" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS56" s="3" t="inlineStr">
@@ -11767,10 +11735,8 @@
           <t>Rohit kumar</t>
         </is>
       </c>
-      <c r="O57" s="3" t="inlineStr">
-        <is>
-          <t>9849109425</t>
-        </is>
+      <c r="O57" s="3" t="n">
+        <v>9849109425</v>
       </c>
       <c r="P57" s="3" t="inlineStr">
         <is>
@@ -11856,10 +11822,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN57" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN57" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO57" s="3" t="inlineStr">
         <is>
@@ -11870,7 +11834,7 @@
       <c r="AQ57" s="3" t="inlineStr"/>
       <c r="AR57" s="3" t="inlineStr">
         <is>
-          <t>Case : Frequent disconnection   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS57" s="3" t="inlineStr">
@@ -11971,10 +11935,8 @@
           <t>Ekta Jagodia</t>
         </is>
       </c>
-      <c r="O58" s="3" t="inlineStr">
-        <is>
-          <t>9802075001</t>
-        </is>
+      <c r="O58" s="3" t="n">
+        <v>9802075001</v>
       </c>
       <c r="P58" s="3" t="inlineStr">
         <is>
@@ -12009,10 +11971,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y58" s="3" t="inlineStr">
-        <is>
-          <t>27.70343</t>
-        </is>
+      <c r="Y58" s="3" t="n">
+        <v>27.70343</v>
       </c>
       <c r="Z58" s="3" t="inlineStr">
         <is>
@@ -12068,55 +12028,1095 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN58" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN58" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO58" s="3" t="inlineStr">
         <is>
           <t>CDB052</t>
         </is>
       </c>
-      <c r="AP58" s="3" t="inlineStr">
-        <is>
-          <t>85.3345</t>
-        </is>
+      <c r="AP58" s="3" t="n">
+        <v>85.33450000000001</v>
       </c>
       <c r="AQ58" s="3" t="inlineStr"/>
       <c r="AR58" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS58" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT58" s="3" t="inlineStr">
+        <is>
+          <t>4h 14m</t>
+        </is>
+      </c>
+      <c r="AU58" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV58" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS58" s="3" t="inlineStr">
+      <c r="AW58" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX58" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 4:00 PM</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr"/>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352419</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>Nishant Subedi</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
+          <t>Nishant Subedi</t>
+        </is>
+      </c>
+      <c r="O59" s="3" t="inlineStr">
+        <is>
+          <t>9847484207</t>
+        </is>
+      </c>
+      <c r="P59" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q59" s="3" t="inlineStr"/>
+      <c r="R59" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 04:00:39 PM</t>
+        </is>
+      </c>
+      <c r="S59" s="3" t="inlineStr"/>
+      <c r="T59" s="3" t="inlineStr"/>
+      <c r="U59" s="3" t="inlineStr">
+        <is>
+          <t>9847484207</t>
+        </is>
+      </c>
+      <c r="V59" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 11:10:05 AM</t>
+        </is>
+      </c>
+      <c r="W59" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 04:00:39 PM</t>
+        </is>
+      </c>
+      <c r="X59" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y59" s="3" t="inlineStr"/>
+      <c r="Z59" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA59" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB59" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC59" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD59" s="3" t="inlineStr"/>
+      <c r="AE59" s="3" t="inlineStr">
+        <is>
+          <t>Near By Monastic Public English School - School M9WF+QQF Unnamed Road Kageshwori Manohara 44600, Bag</t>
+        </is>
+      </c>
+      <c r="AF59" s="3" t="inlineStr"/>
+      <c r="AG59" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH59" s="3" t="inlineStr"/>
+      <c r="AI59" s="3" t="inlineStr">
+        <is>
+          <t>04:50 hour</t>
+        </is>
+      </c>
+      <c r="AJ59" s="3" t="inlineStr"/>
+      <c r="AK59" s="3" t="inlineStr"/>
+      <c r="AL59" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM59" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN59" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO59" s="3" t="inlineStr">
+        <is>
+          <t>4,13</t>
+        </is>
+      </c>
+      <c r="AP59" s="3" t="inlineStr"/>
+      <c r="AQ59" s="3" t="inlineStr"/>
+      <c r="AR59" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS59" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT58" s="3" t="inlineStr">
-        <is>
-          <t>4h 14m</t>
-        </is>
-      </c>
-      <c r="AU58" s="3" t="inlineStr">
+      <c r="AT59" s="3" t="inlineStr">
+        <is>
+          <t>4h 50m</t>
+        </is>
+      </c>
+      <c r="AU59" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV58" s="3" t="inlineStr">
+      <c r="AV59" s="3" t="inlineStr">
         <is>
           <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AW58" s="3" t="inlineStr">
+      <c r="AW59" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX58" s="3" t="inlineStr">
+      <c r="AX59" s="3" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 4:01 PM</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr"/>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>WIFI 6</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351456</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>Puja Regmi</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
+          <t>Puja Regmi</t>
+        </is>
+      </c>
+      <c r="O60" s="3" t="inlineStr">
+        <is>
+          <t>9843038600</t>
+        </is>
+      </c>
+      <c r="P60" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q60" s="3" t="inlineStr"/>
+      <c r="R60" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:48:59 PM</t>
+        </is>
+      </c>
+      <c r="S60" s="3" t="inlineStr"/>
+      <c r="T60" s="3" t="inlineStr"/>
+      <c r="U60" s="3" t="inlineStr">
+        <is>
+          <t>9843038600</t>
+        </is>
+      </c>
+      <c r="V60" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:48:59 PM</t>
+        </is>
+      </c>
+      <c r="W60" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 04:01:18 PM</t>
+        </is>
+      </c>
+      <c r="X60" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y60" s="3" t="inlineStr"/>
+      <c r="Z60" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA60" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB60" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC60" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD60" s="3" t="inlineStr"/>
+      <c r="AE60" s="3" t="inlineStr">
+        <is>
+          <t>Swimming Pool Marg Lalitpur 44700, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF60" s="3" t="inlineStr"/>
+      <c r="AG60" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH60" s="3" t="inlineStr"/>
+      <c r="AI60" s="3" t="inlineStr"/>
+      <c r="AJ60" s="3" t="inlineStr"/>
+      <c r="AK60" s="3" t="inlineStr"/>
+      <c r="AL60" s="3" t="inlineStr">
+        <is>
+          <t>Puja Khadka</t>
+        </is>
+      </c>
+      <c r="AM60" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN60" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO60" s="3" t="inlineStr">
+        <is>
+          <t>1,12</t>
+        </is>
+      </c>
+      <c r="AP60" s="3" t="inlineStr"/>
+      <c r="AQ60" s="3" t="inlineStr"/>
+      <c r="AR60" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS60" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 12m</t>
+        </is>
+      </c>
+      <c r="AT60" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 12m</t>
+        </is>
+      </c>
+      <c r="AU60" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV60" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW60" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX60" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 3:55 PM</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr"/>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>TKT1349829</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>Erish Maharjan</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
+          <t>Erish Maharjan</t>
+        </is>
+      </c>
+      <c r="O61" s="3" t="inlineStr">
+        <is>
+          <t>9808769035</t>
+        </is>
+      </c>
+      <c r="P61" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q61" s="3" t="inlineStr"/>
+      <c r="R61" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 12:20:42 PM</t>
+        </is>
+      </c>
+      <c r="S61" s="3" t="inlineStr"/>
+      <c r="T61" s="3" t="inlineStr"/>
+      <c r="U61" s="3" t="inlineStr">
+        <is>
+          <t>9841424930</t>
+        </is>
+      </c>
+      <c r="V61" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 12:20:42 PM</t>
+        </is>
+      </c>
+      <c r="W61" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 03:55:23 PM</t>
+        </is>
+      </c>
+      <c r="X61" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y61" s="3" t="inlineStr">
+        <is>
+          <t>27.702088</t>
+        </is>
+      </c>
+      <c r="Z61" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA61" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB61" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC61" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD61" s="3" t="inlineStr"/>
+      <c r="AE61" s="3" t="inlineStr">
+        <is>
+          <t>P826+RQP, Kathmandu Near By Sankata Mandir, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF61" s="3" t="inlineStr">
+        <is>
+          <t>lalitamaharjan4@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG61" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH61" s="3" t="inlineStr"/>
+      <c r="AI61" s="3" t="inlineStr">
+        <is>
+          <t>23:35 hour</t>
+        </is>
+      </c>
+      <c r="AJ61" s="3" t="inlineStr"/>
+      <c r="AK61" s="3" t="inlineStr"/>
+      <c r="AL61" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM61" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN61" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO61" s="3" t="inlineStr">
+        <is>
+          <t>1,15</t>
+        </is>
+      </c>
+      <c r="AP61" s="3" t="inlineStr">
+        <is>
+          <t>85.311953</t>
+        </is>
+      </c>
+      <c r="AQ61" s="3" t="inlineStr"/>
+      <c r="AR61" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS61" s="3" t="inlineStr">
+        <is>
+          <t>2d 3h 34m</t>
+        </is>
+      </c>
+      <c r="AT61" s="3" t="inlineStr">
+        <is>
+          <t>2d 3h 34m</t>
+        </is>
+      </c>
+      <c r="AU61" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV61" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW61" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX61" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 3:48 PM</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr"/>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352004</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>Ram Lakhan Sharma</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
+          <t>Ram Lakhan Sharma</t>
+        </is>
+      </c>
+      <c r="O62" s="3" t="inlineStr">
+        <is>
+          <t>9851153192</t>
+        </is>
+      </c>
+      <c r="P62" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q62" s="3" t="inlineStr"/>
+      <c r="R62" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 08:44:43 PM</t>
+        </is>
+      </c>
+      <c r="S62" s="3" t="inlineStr"/>
+      <c r="T62" s="3" t="inlineStr"/>
+      <c r="U62" s="3" t="inlineStr">
+        <is>
+          <t>9851153192</t>
+        </is>
+      </c>
+      <c r="V62" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 08:44:43 PM</t>
+        </is>
+      </c>
+      <c r="W62" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 03:48:02 PM</t>
+        </is>
+      </c>
+      <c r="X62" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y62" s="3" t="inlineStr">
+        <is>
+          <t>27.70276</t>
+        </is>
+      </c>
+      <c r="Z62" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA62" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB62" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC62" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD62" s="3" t="inlineStr"/>
+      <c r="AE62" s="3" t="inlineStr">
+        <is>
+          <t>Syuchatar Pati Chowk,Syuchatar, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF62" s="3" t="inlineStr"/>
+      <c r="AG62" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH62" s="3" t="inlineStr"/>
+      <c r="AI62" s="3" t="inlineStr">
+        <is>
+          <t>05:47 hour</t>
+        </is>
+      </c>
+      <c r="AJ62" s="3" t="inlineStr"/>
+      <c r="AK62" s="3" t="inlineStr"/>
+      <c r="AL62" s="3" t="inlineStr">
+        <is>
+          <t>Ishlok Shahi</t>
+        </is>
+      </c>
+      <c r="AM62" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN62" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO62" s="3" t="inlineStr">
+        <is>
+          <t>CDB201</t>
+        </is>
+      </c>
+      <c r="AP62" s="3" t="inlineStr">
+        <is>
+          <t>85.27484</t>
+        </is>
+      </c>
+      <c r="AQ62" s="3" t="inlineStr"/>
+      <c r="AR62" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS62" s="3" t="inlineStr">
+        <is>
+          <t>19h 3m</t>
+        </is>
+      </c>
+      <c r="AT62" s="3" t="inlineStr">
+        <is>
+          <t>19h 3m</t>
+        </is>
+      </c>
+      <c r="AU62" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV62" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW62" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX62" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 3:47 PM</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr"/>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352004</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>Ram Lakhan Sharma</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
+          <t>Ram Lakhan Sharma</t>
+        </is>
+      </c>
+      <c r="O63" s="3" t="inlineStr">
+        <is>
+          <t>9851153192</t>
+        </is>
+      </c>
+      <c r="P63" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q63" s="3" t="inlineStr"/>
+      <c r="R63" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 08:44:43 PM</t>
+        </is>
+      </c>
+      <c r="S63" s="3" t="inlineStr"/>
+      <c r="T63" s="3" t="inlineStr"/>
+      <c r="U63" s="3" t="inlineStr">
+        <is>
+          <t>9851153192</t>
+        </is>
+      </c>
+      <c r="V63" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 08:44:43 PM</t>
+        </is>
+      </c>
+      <c r="W63" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 03:48:02 PM</t>
+        </is>
+      </c>
+      <c r="X63" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y63" s="3" t="inlineStr">
+        <is>
+          <t>27.70276</t>
+        </is>
+      </c>
+      <c r="Z63" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA63" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB63" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC63" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD63" s="3" t="inlineStr"/>
+      <c r="AE63" s="3" t="inlineStr">
+        <is>
+          <t>Syuchatar Pati Chowk,Syuchatar, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF63" s="3" t="inlineStr"/>
+      <c r="AG63" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH63" s="3" t="inlineStr"/>
+      <c r="AI63" s="3" t="inlineStr">
+        <is>
+          <t>05:47 hour</t>
+        </is>
+      </c>
+      <c r="AJ63" s="3" t="inlineStr"/>
+      <c r="AK63" s="3" t="inlineStr"/>
+      <c r="AL63" s="3" t="inlineStr">
+        <is>
+          <t>Ishlok Shahi</t>
+        </is>
+      </c>
+      <c r="AM63" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN63" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO63" s="3" t="inlineStr">
+        <is>
+          <t>CDB201</t>
+        </is>
+      </c>
+      <c r="AP63" s="3" t="inlineStr">
+        <is>
+          <t>85.27484</t>
+        </is>
+      </c>
+      <c r="AQ63" s="3" t="inlineStr"/>
+      <c r="AR63" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS63" s="3" t="inlineStr">
+        <is>
+          <t>19h 3m</t>
+        </is>
+      </c>
+      <c r="AT63" s="3" t="inlineStr">
+        <is>
+          <t>19h 3m</t>
+        </is>
+      </c>
+      <c r="AU63" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV63" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW63" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX63" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>69.8%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>19.0%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>82.1%</t>
+          <t>82.5%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>63.5%</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>9</v>
@@ -859,7 +859,7 @@
         <v>7</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">
@@ -1012,7 +1012,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>10</v>
@@ -1027,7 +1027,7 @@
         <v>8</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1041,7 +1041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX63"/>
+  <dimension ref="A1:AX64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -12143,10 +12143,8 @@
           <t>Nishant Subedi</t>
         </is>
       </c>
-      <c r="O59" s="3" t="inlineStr">
-        <is>
-          <t>9847484207</t>
-        </is>
+      <c r="O59" s="3" t="n">
+        <v>9847484207</v>
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
@@ -12232,10 +12230,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN59" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN59" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO59" s="3" t="inlineStr">
         <is>
@@ -12246,7 +12242,7 @@
       <c r="AQ59" s="3" t="inlineStr"/>
       <c r="AR59" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS59" s="3" t="inlineStr">
@@ -12347,10 +12343,8 @@
           <t>Puja Regmi</t>
         </is>
       </c>
-      <c r="O60" s="3" t="inlineStr">
-        <is>
-          <t>9843038600</t>
-        </is>
+      <c r="O60" s="3" t="n">
+        <v>9843038600</v>
       </c>
       <c r="P60" s="3" t="inlineStr">
         <is>
@@ -12432,10 +12426,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN60" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN60" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO60" s="3" t="inlineStr">
         <is>
@@ -12446,7 +12438,7 @@
       <c r="AQ60" s="3" t="inlineStr"/>
       <c r="AR60" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS60" s="3" t="inlineStr">
@@ -12547,10 +12539,8 @@
           <t>Erish Maharjan</t>
         </is>
       </c>
-      <c r="O61" s="3" t="inlineStr">
-        <is>
-          <t>9808769035</t>
-        </is>
+      <c r="O61" s="3" t="n">
+        <v>9808769035</v>
       </c>
       <c r="P61" s="3" t="inlineStr">
         <is>
@@ -12585,10 +12575,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y61" s="3" t="inlineStr">
-        <is>
-          <t>27.702088</t>
-        </is>
+      <c r="Y61" s="3" t="n">
+        <v>27.702088</v>
       </c>
       <c r="Z61" s="3" t="inlineStr">
         <is>
@@ -12644,25 +12632,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN61" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN61" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO61" s="3" t="inlineStr">
         <is>
           <t>1,15</t>
         </is>
       </c>
-      <c r="AP61" s="3" t="inlineStr">
-        <is>
-          <t>85.311953</t>
-        </is>
+      <c r="AP61" s="3" t="n">
+        <v>85.311953</v>
       </c>
       <c r="AQ61" s="3" t="inlineStr"/>
       <c r="AR61" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS61" s="3" t="inlineStr">
@@ -12753,20 +12737,14 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="M62" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M62" s="3" t="inlineStr"/>
       <c r="N62" s="3" t="inlineStr">
         <is>
           <t>Ram Lakhan Sharma</t>
         </is>
       </c>
-      <c r="O62" s="3" t="inlineStr">
-        <is>
-          <t>9851153192</t>
-        </is>
+      <c r="O62" s="3" t="n">
+        <v>9851153192</v>
       </c>
       <c r="P62" s="3" t="inlineStr">
         <is>
@@ -12801,10 +12779,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y62" s="3" t="inlineStr">
-        <is>
-          <t>27.70276</t>
-        </is>
+      <c r="Y62" s="3" t="n">
+        <v>27.70276</v>
       </c>
       <c r="Z62" s="3" t="inlineStr">
         <is>
@@ -12856,25 +12832,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN62" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN62" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO62" s="3" t="inlineStr">
         <is>
           <t>CDB201</t>
         </is>
       </c>
-      <c r="AP62" s="3" t="inlineStr">
-        <is>
-          <t>85.27484</t>
-        </is>
+      <c r="AP62" s="3" t="n">
+        <v>85.27484</v>
       </c>
       <c r="AQ62" s="3" t="inlineStr"/>
       <c r="AR62" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS62" s="3" t="inlineStr">
@@ -12965,20 +12937,14 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="M63" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M63" s="3" t="inlineStr"/>
       <c r="N63" s="3" t="inlineStr">
         <is>
           <t>Ram Lakhan Sharma</t>
         </is>
       </c>
-      <c r="O63" s="3" t="inlineStr">
-        <is>
-          <t>9851153192</t>
-        </is>
+      <c r="O63" s="3" t="n">
+        <v>9851153192</v>
       </c>
       <c r="P63" s="3" t="inlineStr">
         <is>
@@ -13013,10 +12979,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y63" s="3" t="inlineStr">
-        <is>
-          <t>27.70276</t>
-        </is>
+      <c r="Y63" s="3" t="n">
+        <v>27.70276</v>
       </c>
       <c r="Z63" s="3" t="inlineStr">
         <is>
@@ -13068,47 +13032,43 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN63" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN63" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO63" s="3" t="inlineStr">
         <is>
           <t>CDB201</t>
         </is>
       </c>
-      <c r="AP63" s="3" t="inlineStr">
-        <is>
-          <t>85.27484</t>
-        </is>
+      <c r="AP63" s="3" t="n">
+        <v>85.27484</v>
       </c>
       <c r="AQ63" s="3" t="inlineStr"/>
       <c r="AR63" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS63" s="3" t="inlineStr">
+        <is>
+          <t>19h 3m</t>
+        </is>
+      </c>
+      <c r="AT63" s="3" t="inlineStr">
+        <is>
+          <t>19h 3m</t>
+        </is>
+      </c>
+      <c r="AU63" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV63" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS63" s="3" t="inlineStr">
-        <is>
-          <t>19h 3m</t>
-        </is>
-      </c>
-      <c r="AT63" s="3" t="inlineStr">
-        <is>
-          <t>19h 3m</t>
-        </is>
-      </c>
-      <c r="AU63" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV63" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW63" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -13117,6 +13077,222 @@
       <c r="AX63" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 4:06 PM</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr"/>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352477</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>Pradyot Rana</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
+          <t>Pradyot Rana</t>
+        </is>
+      </c>
+      <c r="O64" s="3" t="inlineStr">
+        <is>
+          <t>9801082074</t>
+        </is>
+      </c>
+      <c r="P64" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q64" s="3" t="inlineStr"/>
+      <c r="R64" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 04:06:35 PM</t>
+        </is>
+      </c>
+      <c r="S64" s="3" t="inlineStr"/>
+      <c r="T64" s="3" t="inlineStr"/>
+      <c r="U64" s="3" t="inlineStr">
+        <is>
+          <t>pradyotrana</t>
+        </is>
+      </c>
+      <c r="V64" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 11:44:42 AM</t>
+        </is>
+      </c>
+      <c r="W64" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 04:06:35 PM</t>
+        </is>
+      </c>
+      <c r="X64" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y64" s="3" t="inlineStr">
+        <is>
+          <t>27.66681</t>
+        </is>
+      </c>
+      <c r="Z64" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA64" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB64" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC64" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD64" s="3" t="inlineStr"/>
+      <c r="AE64" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur-5,Manbhawan,Backside of Distirct Administarion office , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF64" s="3" t="inlineStr">
+        <is>
+          <t>pradyotrana@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG64" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH64" s="3" t="inlineStr"/>
+      <c r="AI64" s="3" t="inlineStr">
+        <is>
+          <t>04:22 hour</t>
+        </is>
+      </c>
+      <c r="AJ64" s="3" t="inlineStr"/>
+      <c r="AK64" s="3" t="inlineStr"/>
+      <c r="AL64" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM64" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN64" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO64" s="3" t="inlineStr">
+        <is>
+          <t>2,13</t>
+        </is>
+      </c>
+      <c r="AP64" s="3" t="inlineStr">
+        <is>
+          <t>85.31694</t>
+        </is>
+      </c>
+      <c r="AQ64" s="3" t="inlineStr"/>
+      <c r="AR64" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS64" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT64" s="3" t="inlineStr">
+        <is>
+          <t>4h 21m</t>
+        </is>
+      </c>
+      <c r="AU64" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV64" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW64" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX64" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>70.3%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>11</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>20.3%</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -1015,7 +1015,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>8</v>
@@ -1027,7 +1027,7 @@
         <v>8</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1041,7 +1041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX64"/>
+  <dimension ref="A1:AX65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -13147,10 +13147,8 @@
           <t>Pradyot Rana</t>
         </is>
       </c>
-      <c r="O64" s="3" t="inlineStr">
-        <is>
-          <t>9801082074</t>
-        </is>
+      <c r="O64" s="3" t="n">
+        <v>9801082074</v>
       </c>
       <c r="P64" s="3" t="inlineStr">
         <is>
@@ -13185,10 +13183,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y64" s="3" t="inlineStr">
-        <is>
-          <t>27.66681</t>
-        </is>
+      <c r="Y64" s="3" t="n">
+        <v>27.66681</v>
       </c>
       <c r="Z64" s="3" t="inlineStr">
         <is>
@@ -13244,55 +13240,259 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN64" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN64" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO64" s="3" t="inlineStr">
         <is>
           <t>2,13</t>
         </is>
       </c>
-      <c r="AP64" s="3" t="inlineStr">
-        <is>
-          <t>85.31694</t>
-        </is>
+      <c r="AP64" s="3" t="n">
+        <v>85.31694</v>
       </c>
       <c r="AQ64" s="3" t="inlineStr"/>
       <c r="AR64" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS64" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT64" s="3" t="inlineStr">
+        <is>
+          <t>4h 21m</t>
+        </is>
+      </c>
+      <c r="AU64" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV64" s="3" t="inlineStr">
+        <is>
           <t>Case : Wi-Fi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS64" s="3" t="inlineStr">
+      <c r="AW64" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX64" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 4:12 PM</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr"/>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>Case : ssid hide   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>ssid hide</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351502</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>kamala kharel</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
+          <t>kamala kharel</t>
+        </is>
+      </c>
+      <c r="O65" s="3" t="inlineStr">
+        <is>
+          <t>9862408918</t>
+        </is>
+      </c>
+      <c r="P65" s="3" t="inlineStr">
+        <is>
+          <t>Frequent Internet Disconnection</t>
+        </is>
+      </c>
+      <c r="Q65" s="3" t="inlineStr"/>
+      <c r="R65" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 04:12:08 PM</t>
+        </is>
+      </c>
+      <c r="S65" s="3" t="inlineStr"/>
+      <c r="T65" s="3" t="inlineStr"/>
+      <c r="U65" s="3" t="inlineStr">
+        <is>
+          <t>9862408918</t>
+        </is>
+      </c>
+      <c r="V65" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 02:25:44 PM</t>
+        </is>
+      </c>
+      <c r="W65" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 04:12:08 PM</t>
+        </is>
+      </c>
+      <c r="X65" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y65" s="3" t="inlineStr"/>
+      <c r="Z65" s="3" t="inlineStr">
+        <is>
+          <t>Frequent Internet Disconnection</t>
+        </is>
+      </c>
+      <c r="AA65" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB65" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC65" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD65" s="3" t="inlineStr"/>
+      <c r="AE65" s="3" t="inlineStr">
+        <is>
+          <t>Kageshwori Manohara 44600 near by Force Park Bus Stop - Bus stop, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF65" s="3" t="inlineStr">
+        <is>
+          <t>mainailiraj45@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG65" s="3" t="inlineStr">
+        <is>
+          <t>Due to Configuration Issue</t>
+        </is>
+      </c>
+      <c r="AH65" s="3" t="inlineStr"/>
+      <c r="AI65" s="3" t="inlineStr">
+        <is>
+          <t>11:47 hour</t>
+        </is>
+      </c>
+      <c r="AJ65" s="3" t="inlineStr"/>
+      <c r="AK65" s="3" t="inlineStr"/>
+      <c r="AL65" s="3" t="inlineStr">
+        <is>
+          <t>Manisha kunwar</t>
+        </is>
+      </c>
+      <c r="AM65" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN65" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO65" s="3" t="inlineStr">
+        <is>
+          <t>L56-3</t>
+        </is>
+      </c>
+      <c r="AP65" s="3" t="inlineStr"/>
+      <c r="AQ65" s="3" t="inlineStr"/>
+      <c r="AR65" s="3" t="inlineStr">
+        <is>
+          <t>Case : ssid hide   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS65" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT64" s="3" t="inlineStr">
-        <is>
-          <t>4h 21m</t>
-        </is>
-      </c>
-      <c r="AU64" s="3" t="inlineStr">
+      <c r="AT65" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 46m</t>
+        </is>
+      </c>
+      <c r="AU65" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV64" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wi-Fi 6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="AW64" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
-        </is>
-      </c>
-      <c r="AX64" s="3" t="inlineStr">
-        <is>
-          <t>Rajesh Maharjan</t>
+      <c r="AV65" s="3" t="inlineStr">
+        <is>
+          <t>Case : ssid hide   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW65" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX65" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
@@ -1087,7 +1087,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -13355,10 +13355,8 @@
           <t>kamala kharel</t>
         </is>
       </c>
-      <c r="O65" s="3" t="inlineStr">
-        <is>
-          <t>9862408918</t>
-        </is>
+      <c r="O65" s="3" t="n">
+        <v>9862408918</v>
       </c>
       <c r="P65" s="3" t="inlineStr">
         <is>
@@ -13448,10 +13446,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN65" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN65" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO65" s="3" t="inlineStr">
         <is>
@@ -13462,7 +13458,7 @@
       <c r="AQ65" s="3" t="inlineStr"/>
       <c r="AR65" s="3" t="inlineStr">
         <is>
-          <t>Case : ssid hide   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS65" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>58.3%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>70.8%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>12</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>92.9%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>21.5%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>1.5%</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>61.5%</t>
         </is>
       </c>
     </row>
@@ -853,13 +853,13 @@
         <v>3</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>7</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
@@ -1021,13 +1021,13 @@
         <v>8</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>8</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1041,7 +1041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX65"/>
+  <dimension ref="A1:AX66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1087,7 +1087,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -13492,6 +13492,222 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 4:54 PM</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr"/>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>Router upgrade</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351443</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>Ramesh Chaudhary</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
+          <t>Ramesh Chaudhary</t>
+        </is>
+      </c>
+      <c r="O66" s="3" t="inlineStr">
+        <is>
+          <t>9818114292</t>
+        </is>
+      </c>
+      <c r="P66" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q66" s="3" t="inlineStr"/>
+      <c r="R66" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:42:26 PM</t>
+        </is>
+      </c>
+      <c r="S66" s="3" t="inlineStr"/>
+      <c r="T66" s="3" t="inlineStr"/>
+      <c r="U66" s="3" t="inlineStr">
+        <is>
+          <t>9818114292</t>
+        </is>
+      </c>
+      <c r="V66" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:42:26 PM</t>
+        </is>
+      </c>
+      <c r="W66" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 04:54:13 PM</t>
+        </is>
+      </c>
+      <c r="X66" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y66" s="3" t="inlineStr">
+        <is>
+          <t>27.68282</t>
+        </is>
+      </c>
+      <c r="Z66" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA66" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB66" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC66" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD66" s="3" t="inlineStr"/>
+      <c r="AE66" s="3" t="inlineStr">
+        <is>
+          <t>Inside Pulchwok campus, Way from Jwagal Banquet,Pulchwok,Lalitpur-10, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF66" s="3" t="inlineStr">
+        <is>
+          <t>ioeramesh@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG66" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH66" s="3" t="inlineStr"/>
+      <c r="AI66" s="3" t="inlineStr">
+        <is>
+          <t>13:12 hour</t>
+        </is>
+      </c>
+      <c r="AJ66" s="3" t="inlineStr"/>
+      <c r="AK66" s="3" t="inlineStr"/>
+      <c r="AL66" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM66" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN66" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO66" s="3" t="inlineStr">
+        <is>
+          <t>2,10</t>
+        </is>
+      </c>
+      <c r="AP66" s="3" t="inlineStr">
+        <is>
+          <t>85.3247</t>
+        </is>
+      </c>
+      <c r="AQ66" s="3" t="inlineStr"/>
+      <c r="AR66" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS66" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 11m</t>
+        </is>
+      </c>
+      <c r="AT66" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 11m</t>
+        </is>
+      </c>
+      <c r="AU66" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV66" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW66" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX66" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
@@ -1087,7 +1087,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -13559,10 +13559,8 @@
           <t>Ramesh Chaudhary</t>
         </is>
       </c>
-      <c r="O66" s="3" t="inlineStr">
-        <is>
-          <t>9818114292</t>
-        </is>
+      <c r="O66" s="3" t="n">
+        <v>9818114292</v>
       </c>
       <c r="P66" s="3" t="inlineStr">
         <is>
@@ -13597,10 +13595,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y66" s="3" t="inlineStr">
-        <is>
-          <t>27.68282</t>
-        </is>
+      <c r="Y66" s="3" t="n">
+        <v>27.68282</v>
       </c>
       <c r="Z66" s="3" t="inlineStr">
         <is>
@@ -13656,25 +13652,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN66" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN66" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO66" s="3" t="inlineStr">
         <is>
           <t>2,10</t>
         </is>
       </c>
-      <c r="AP66" s="3" t="inlineStr">
-        <is>
-          <t>85.3247</t>
-        </is>
+      <c r="AP66" s="3" t="n">
+        <v>85.32470000000001</v>
       </c>
       <c r="AQ66" s="3" t="inlineStr"/>
       <c r="AR66" s="3" t="inlineStr">
         <is>
-          <t>Case : Router upgrade   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS66" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>71.6%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>20.9%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>82.5%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>62.7%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>9</v>
@@ -859,7 +859,7 @@
         <v>7</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3">
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>9</v>
@@ -1027,7 +1027,7 @@
         <v>8</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1041,7 +1041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX66"/>
+  <dimension ref="A1:AX68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1087,7 +1087,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -13700,6 +13700,430 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 5:17 PM</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr"/>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351750</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>Pushpa Raj Gelal</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
+          <t>Pushpa Raj Gelal</t>
+        </is>
+      </c>
+      <c r="O67" s="3" t="inlineStr">
+        <is>
+          <t>9851048369</t>
+        </is>
+      </c>
+      <c r="P67" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q67" s="3" t="inlineStr"/>
+      <c r="R67" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 05:12:06 PM</t>
+        </is>
+      </c>
+      <c r="S67" s="3" t="inlineStr"/>
+      <c r="T67" s="3" t="inlineStr"/>
+      <c r="U67" s="3" t="inlineStr">
+        <is>
+          <t>9851048369</t>
+        </is>
+      </c>
+      <c r="V67" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 05:12:06 PM</t>
+        </is>
+      </c>
+      <c r="W67" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 05:17:01 PM</t>
+        </is>
+      </c>
+      <c r="X67" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y67" s="3" t="inlineStr">
+        <is>
+          <t>27.701238</t>
+        </is>
+      </c>
+      <c r="Z67" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA67" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB67" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC67" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD67" s="3" t="inlineStr"/>
+      <c r="AE67" s="3" t="inlineStr">
+        <is>
+          <t>P825+F6W Kathmandu, Jhochhen, Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF67" s="3" t="inlineStr"/>
+      <c r="AG67" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH67" s="3" t="inlineStr"/>
+      <c r="AI67" s="3" t="inlineStr">
+        <is>
+          <t>10:03 hour</t>
+        </is>
+      </c>
+      <c r="AJ67" s="3" t="inlineStr"/>
+      <c r="AK67" s="3" t="inlineStr"/>
+      <c r="AL67" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM67" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN67" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO67" s="3" t="inlineStr">
+        <is>
+          <t>1,4</t>
+        </is>
+      </c>
+      <c r="AP67" s="3" t="inlineStr">
+        <is>
+          <t>85.308078</t>
+        </is>
+      </c>
+      <c r="AQ67" s="3" t="inlineStr"/>
+      <c r="AR67" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS67" s="3" t="inlineStr">
+        <is>
+          <t>1d 4m</t>
+        </is>
+      </c>
+      <c r="AT67" s="3" t="inlineStr">
+        <is>
+          <t>1d 4m</t>
+        </is>
+      </c>
+      <c r="AU67" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV67" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW67" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX67" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 5:15 PM</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr"/>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351750</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>Pushpa Raj Gelal</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
+          <t>Pushpa Raj Gelal</t>
+        </is>
+      </c>
+      <c r="O68" s="3" t="inlineStr">
+        <is>
+          <t>9851048369</t>
+        </is>
+      </c>
+      <c r="P68" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q68" s="3" t="inlineStr"/>
+      <c r="R68" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 05:12:06 PM</t>
+        </is>
+      </c>
+      <c r="S68" s="3" t="inlineStr"/>
+      <c r="T68" s="3" t="inlineStr"/>
+      <c r="U68" s="3" t="inlineStr">
+        <is>
+          <t>9851048369</t>
+        </is>
+      </c>
+      <c r="V68" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 05:12:06 PM</t>
+        </is>
+      </c>
+      <c r="W68" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 05:17:01 PM</t>
+        </is>
+      </c>
+      <c r="X68" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y68" s="3" t="inlineStr">
+        <is>
+          <t>27.701238</t>
+        </is>
+      </c>
+      <c r="Z68" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA68" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB68" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC68" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD68" s="3" t="inlineStr"/>
+      <c r="AE68" s="3" t="inlineStr">
+        <is>
+          <t>P825+F6W Kathmandu, Jhochhen, Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF68" s="3" t="inlineStr"/>
+      <c r="AG68" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH68" s="3" t="inlineStr"/>
+      <c r="AI68" s="3" t="inlineStr">
+        <is>
+          <t>10:03 hour</t>
+        </is>
+      </c>
+      <c r="AJ68" s="3" t="inlineStr"/>
+      <c r="AK68" s="3" t="inlineStr"/>
+      <c r="AL68" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM68" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN68" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO68" s="3" t="inlineStr">
+        <is>
+          <t>1,4</t>
+        </is>
+      </c>
+      <c r="AP68" s="3" t="inlineStr">
+        <is>
+          <t>85.308078</t>
+        </is>
+      </c>
+      <c r="AQ68" s="3" t="inlineStr"/>
+      <c r="AR68" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS68" s="3" t="inlineStr">
+        <is>
+          <t>1d 4m</t>
+        </is>
+      </c>
+      <c r="AT68" s="3" t="inlineStr">
+        <is>
+          <t>1d 4m</t>
+        </is>
+      </c>
+      <c r="AU68" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV68" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW68" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX68" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
@@ -1087,7 +1087,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -13767,10 +13767,8 @@
           <t>Pushpa Raj Gelal</t>
         </is>
       </c>
-      <c r="O67" s="3" t="inlineStr">
-        <is>
-          <t>9851048369</t>
-        </is>
+      <c r="O67" s="3" t="n">
+        <v>9851048369</v>
       </c>
       <c r="P67" s="3" t="inlineStr">
         <is>
@@ -13805,10 +13803,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y67" s="3" t="inlineStr">
-        <is>
-          <t>27.701238</t>
-        </is>
+      <c r="Y67" s="3" t="n">
+        <v>27.701238</v>
       </c>
       <c r="Z67" s="3" t="inlineStr">
         <is>
@@ -13860,25 +13856,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN67" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN67" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO67" s="3" t="inlineStr">
         <is>
           <t>1,4</t>
         </is>
       </c>
-      <c r="AP67" s="3" t="inlineStr">
-        <is>
-          <t>85.308078</t>
-        </is>
+      <c r="AP67" s="3" t="n">
+        <v>85.30807799999999</v>
       </c>
       <c r="AQ67" s="3" t="inlineStr"/>
       <c r="AR67" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS67" s="3" t="inlineStr">
@@ -13979,10 +13971,8 @@
           <t>Pushpa Raj Gelal</t>
         </is>
       </c>
-      <c r="O68" s="3" t="inlineStr">
-        <is>
-          <t>9851048369</t>
-        </is>
+      <c r="O68" s="3" t="n">
+        <v>9851048369</v>
       </c>
       <c r="P68" s="3" t="inlineStr">
         <is>
@@ -14017,10 +14007,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y68" s="3" t="inlineStr">
-        <is>
-          <t>27.701238</t>
-        </is>
+      <c r="Y68" s="3" t="n">
+        <v>27.701238</v>
       </c>
       <c r="Z68" s="3" t="inlineStr">
         <is>
@@ -14072,25 +14060,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN68" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN68" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO68" s="3" t="inlineStr">
         <is>
           <t>1,4</t>
         </is>
       </c>
-      <c r="AP68" s="3" t="inlineStr">
-        <is>
-          <t>85.308078</t>
-        </is>
+      <c r="AP68" s="3" t="n">
+        <v>85.30807799999999</v>
       </c>
       <c r="AQ68" s="3" t="inlineStr"/>
       <c r="AR68" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS68" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>9</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>69.2%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>69.2%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>61.5%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>71.8%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>13</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>92.9%</t>
+          <t>93.3%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>21.1%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>1.4%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>84.1%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>62.0%</t>
         </is>
       </c>
     </row>
@@ -850,16 +850,16 @@
         <v>9</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>7</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
@@ -1018,16 +1018,16 @@
         <v>11</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>8</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1041,7 +1041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX68"/>
+  <dimension ref="A1:AX72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1087,7 +1087,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -14108,6 +14108,734 @@
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 6:00 PM</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr"/>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352865</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>Niraj Dulal</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
+          <t>Niraj Dulal</t>
+        </is>
+      </c>
+      <c r="O69" s="3" t="inlineStr">
+        <is>
+          <t>9862907359</t>
+        </is>
+      </c>
+      <c r="P69" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q69" s="3" t="inlineStr"/>
+      <c r="R69" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 06:00:16 PM</t>
+        </is>
+      </c>
+      <c r="S69" s="3" t="inlineStr"/>
+      <c r="T69" s="3" t="inlineStr"/>
+      <c r="U69" s="3" t="inlineStr">
+        <is>
+          <t>9862907359</t>
+        </is>
+      </c>
+      <c r="V69" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 03:54:56 PM</t>
+        </is>
+      </c>
+      <c r="W69" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 06:00:16 PM</t>
+        </is>
+      </c>
+      <c r="X69" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y69" s="3" t="inlineStr">
+        <is>
+          <t>27.67418</t>
+        </is>
+      </c>
+      <c r="Z69" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA69" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB69" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC69" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD69" s="3" t="inlineStr"/>
+      <c r="AE69" s="3" t="inlineStr">
+        <is>
+          <t>Dental clinic(summit hospital) , Unnamed Road, M9F5+JW6, ??????? ???? , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF69" s="3" t="inlineStr"/>
+      <c r="AG69" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH69" s="3" t="inlineStr"/>
+      <c r="AI69" s="3" t="inlineStr">
+        <is>
+          <t>02:06 hour</t>
+        </is>
+      </c>
+      <c r="AJ69" s="3" t="inlineStr"/>
+      <c r="AK69" s="3" t="inlineStr"/>
+      <c r="AL69" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM69" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN69" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO69" s="3" t="inlineStr">
+        <is>
+          <t>L41-3</t>
+        </is>
+      </c>
+      <c r="AP69" s="3" t="inlineStr">
+        <is>
+          <t>85.358561</t>
+        </is>
+      </c>
+      <c r="AQ69" s="3" t="inlineStr"/>
+      <c r="AR69" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS69" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT69" s="3" t="inlineStr">
+        <is>
+          <t>2h 5m</t>
+        </is>
+      </c>
+      <c r="AU69" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV69" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW69" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX69" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 6:00 PM</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr"/>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352464</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>Tikaram Subedi</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
+          <t>Tikaram Subedi</t>
+        </is>
+      </c>
+      <c r="O70" s="3" t="inlineStr">
+        <is>
+          <t>9851090693</t>
+        </is>
+      </c>
+      <c r="P70" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q70" s="3" t="inlineStr"/>
+      <c r="R70" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 06:00:51 PM</t>
+        </is>
+      </c>
+      <c r="S70" s="3" t="inlineStr"/>
+      <c r="T70" s="3" t="inlineStr"/>
+      <c r="U70" s="3" t="inlineStr">
+        <is>
+          <t>9851090693T</t>
+        </is>
+      </c>
+      <c r="V70" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 11:34:55 AM</t>
+        </is>
+      </c>
+      <c r="W70" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 06:00:51 PM</t>
+        </is>
+      </c>
+      <c r="X70" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y70" s="3" t="inlineStr"/>
+      <c r="Z70" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA70" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB70" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC70" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD70" s="3" t="inlineStr"/>
+      <c r="AE70" s="3" t="inlineStr">
+        <is>
+          <t>Jorpati Near Venus Public School, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF70" s="3" t="inlineStr"/>
+      <c r="AG70" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH70" s="3" t="inlineStr"/>
+      <c r="AI70" s="3" t="inlineStr">
+        <is>
+          <t>06:26 hour</t>
+        </is>
+      </c>
+      <c r="AJ70" s="3" t="inlineStr"/>
+      <c r="AK70" s="3" t="inlineStr"/>
+      <c r="AL70" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM70" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN70" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO70" s="3" t="inlineStr">
+        <is>
+          <t>L42-6</t>
+        </is>
+      </c>
+      <c r="AP70" s="3" t="inlineStr"/>
+      <c r="AQ70" s="3" t="inlineStr"/>
+      <c r="AR70" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS70" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT70" s="3" t="inlineStr">
+        <is>
+          <t>6h 25m</t>
+        </is>
+      </c>
+      <c r="AU70" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV70" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW70" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX70" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 5:16 PM</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr"/>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352464</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>Tikaram Subedi</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
+          <t>Tikaram Subedi</t>
+        </is>
+      </c>
+      <c r="O71" s="3" t="inlineStr">
+        <is>
+          <t>9851090693</t>
+        </is>
+      </c>
+      <c r="P71" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q71" s="3" t="inlineStr"/>
+      <c r="R71" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 06:00:51 PM</t>
+        </is>
+      </c>
+      <c r="S71" s="3" t="inlineStr"/>
+      <c r="T71" s="3" t="inlineStr"/>
+      <c r="U71" s="3" t="inlineStr">
+        <is>
+          <t>9851090693T</t>
+        </is>
+      </c>
+      <c r="V71" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 11:34:55 AM</t>
+        </is>
+      </c>
+      <c r="W71" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 06:00:51 PM</t>
+        </is>
+      </c>
+      <c r="X71" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y71" s="3" t="inlineStr"/>
+      <c r="Z71" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA71" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB71" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC71" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD71" s="3" t="inlineStr"/>
+      <c r="AE71" s="3" t="inlineStr">
+        <is>
+          <t>Jorpati Near Venus Public School, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF71" s="3" t="inlineStr"/>
+      <c r="AG71" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH71" s="3" t="inlineStr"/>
+      <c r="AI71" s="3" t="inlineStr">
+        <is>
+          <t>06:26 hour</t>
+        </is>
+      </c>
+      <c r="AJ71" s="3" t="inlineStr"/>
+      <c r="AK71" s="3" t="inlineStr"/>
+      <c r="AL71" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM71" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN71" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO71" s="3" t="inlineStr">
+        <is>
+          <t>L42-6</t>
+        </is>
+      </c>
+      <c r="AP71" s="3" t="inlineStr"/>
+      <c r="AQ71" s="3" t="inlineStr"/>
+      <c r="AR71" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS71" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT71" s="3" t="inlineStr">
+        <is>
+          <t>6h 25m</t>
+        </is>
+      </c>
+      <c r="AU71" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV71" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW71" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX71" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 5:50 PM</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr"/>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr"/>
+      <c r="J72" s="3" t="inlineStr"/>
+      <c r="K72" s="3" t="inlineStr"/>
+      <c r="L72" s="3" t="inlineStr"/>
+      <c r="M72" s="3" t="inlineStr"/>
+      <c r="N72" s="3" t="inlineStr"/>
+      <c r="O72" s="3" t="inlineStr"/>
+      <c r="P72" s="3" t="inlineStr"/>
+      <c r="Q72" s="3" t="inlineStr"/>
+      <c r="R72" s="3" t="inlineStr"/>
+      <c r="S72" s="3" t="inlineStr"/>
+      <c r="T72" s="3" t="inlineStr"/>
+      <c r="U72" s="3" t="inlineStr"/>
+      <c r="V72" s="3" t="inlineStr"/>
+      <c r="W72" s="3" t="inlineStr"/>
+      <c r="X72" s="3" t="inlineStr"/>
+      <c r="Y72" s="3" t="inlineStr"/>
+      <c r="Z72" s="3" t="inlineStr"/>
+      <c r="AA72" s="3" t="inlineStr"/>
+      <c r="AB72" s="3" t="inlineStr"/>
+      <c r="AC72" s="3" t="inlineStr"/>
+      <c r="AD72" s="3" t="inlineStr"/>
+      <c r="AE72" s="3" t="inlineStr"/>
+      <c r="AF72" s="3" t="inlineStr"/>
+      <c r="AG72" s="3" t="inlineStr"/>
+      <c r="AH72" s="3" t="inlineStr"/>
+      <c r="AI72" s="3" t="inlineStr"/>
+      <c r="AJ72" s="3" t="inlineStr"/>
+      <c r="AK72" s="3" t="inlineStr"/>
+      <c r="AL72" s="3" t="inlineStr"/>
+      <c r="AM72" s="3" t="inlineStr"/>
+      <c r="AN72" s="3" t="inlineStr"/>
+      <c r="AO72" s="3" t="inlineStr"/>
+      <c r="AP72" s="3" t="inlineStr"/>
+      <c r="AQ72" s="3" t="inlineStr"/>
+      <c r="AR72" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS72" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT72" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU72" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV72" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW72" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX72" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>84.6%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>71.8%</t>
+          <t>72.6%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>20.5%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>84.1%</t>
+          <t>84.8%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>63.0%</t>
         </is>
       </c>
     </row>
@@ -844,10 +844,10 @@
         <v>7</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>4</v>
@@ -859,7 +859,7 @@
         <v>7</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3">
@@ -1012,10 +1012,10 @@
         <v>8</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>9</v>
@@ -1027,7 +1027,7 @@
         <v>8</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1041,7 +1041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX72"/>
+  <dimension ref="A1:AX74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -14175,10 +14175,8 @@
           <t>Niraj Dulal</t>
         </is>
       </c>
-      <c r="O69" s="3" t="inlineStr">
-        <is>
-          <t>9862907359</t>
-        </is>
+      <c r="O69" s="3" t="n">
+        <v>9862907359</v>
       </c>
       <c r="P69" s="3" t="inlineStr">
         <is>
@@ -14213,10 +14211,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y69" s="3" t="inlineStr">
-        <is>
-          <t>27.67418</t>
-        </is>
+      <c r="Y69" s="3" t="n">
+        <v>27.67418</v>
       </c>
       <c r="Z69" s="3" t="inlineStr">
         <is>
@@ -14268,25 +14264,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN69" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN69" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO69" s="3" t="inlineStr">
         <is>
           <t>L41-3</t>
         </is>
       </c>
-      <c r="AP69" s="3" t="inlineStr">
-        <is>
-          <t>85.358561</t>
-        </is>
+      <c r="AP69" s="3" t="n">
+        <v>85.35856099999999</v>
       </c>
       <c r="AQ69" s="3" t="inlineStr"/>
       <c r="AR69" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS69" s="3" t="inlineStr">
@@ -14387,10 +14379,8 @@
           <t>Tikaram Subedi</t>
         </is>
       </c>
-      <c r="O70" s="3" t="inlineStr">
-        <is>
-          <t>9851090693</t>
-        </is>
+      <c r="O70" s="3" t="n">
+        <v>9851090693</v>
       </c>
       <c r="P70" s="3" t="inlineStr">
         <is>
@@ -14476,10 +14466,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN70" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN70" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO70" s="3" t="inlineStr">
         <is>
@@ -14490,7 +14478,7 @@
       <c r="AQ70" s="3" t="inlineStr"/>
       <c r="AR70" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS70" s="3" t="inlineStr">
@@ -14591,10 +14579,8 @@
           <t>Tikaram Subedi</t>
         </is>
       </c>
-      <c r="O71" s="3" t="inlineStr">
-        <is>
-          <t>9851090693</t>
-        </is>
+      <c r="O71" s="3" t="n">
+        <v>9851090693</v>
       </c>
       <c r="P71" s="3" t="inlineStr">
         <is>
@@ -14680,10 +14666,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN71" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN71" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO71" s="3" t="inlineStr">
         <is>
@@ -14694,7 +14678,7 @@
       <c r="AQ71" s="3" t="inlineStr"/>
       <c r="AR71" s="3" t="inlineStr">
         <is>
-          <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS71" s="3" t="inlineStr">
@@ -14836,6 +14820,426 @@
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 6:15 PM</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr"/>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>upgrade wifi 6</t>
+        </is>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350430</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>SY Panel  Nepal Ltd</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
+          <t>SY Panel  Nepal Ltd</t>
+        </is>
+      </c>
+      <c r="O73" s="3" t="inlineStr">
+        <is>
+          <t>9851338341</t>
+        </is>
+      </c>
+      <c r="P73" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q73" s="3" t="inlineStr"/>
+      <c r="R73" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 06:15:04 PM</t>
+        </is>
+      </c>
+      <c r="S73" s="3" t="inlineStr"/>
+      <c r="T73" s="3" t="inlineStr"/>
+      <c r="U73" s="3" t="inlineStr">
+        <is>
+          <t>9851338341</t>
+        </is>
+      </c>
+      <c r="V73" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 04:45:12 PM</t>
+        </is>
+      </c>
+      <c r="W73" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 06:15:04 PM</t>
+        </is>
+      </c>
+      <c r="X73" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y73" s="3" t="inlineStr"/>
+      <c r="Z73" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA73" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB73" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC73" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD73" s="3" t="inlineStr"/>
+      <c r="AE73" s="3" t="inlineStr">
+        <is>
+          <t>HIKVISION TOWER - Store HIKVISION NEPAL- TOWER, Budhanilakantha-2 Kathmandu 44600, Bagmati, Nepal, N</t>
+        </is>
+      </c>
+      <c r="AF73" s="3" t="inlineStr">
+        <is>
+          <t>maheshwor12@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG73" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH73" s="3" t="inlineStr"/>
+      <c r="AI73" s="3" t="inlineStr">
+        <is>
+          <t>21:30 hour</t>
+        </is>
+      </c>
+      <c r="AJ73" s="3" t="inlineStr"/>
+      <c r="AK73" s="3" t="inlineStr"/>
+      <c r="AL73" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM73" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN73" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO73" s="3" t="inlineStr">
+        <is>
+          <t>L37-6</t>
+        </is>
+      </c>
+      <c r="AP73" s="3" t="inlineStr"/>
+      <c r="AQ73" s="3" t="inlineStr"/>
+      <c r="AR73" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS73" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT73" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 29m</t>
+        </is>
+      </c>
+      <c r="AU73" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV73" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW73" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX73" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 6:16 PM</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr"/>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352522</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>Binda Adhikari</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
+          <t>Binda Adhikari</t>
+        </is>
+      </c>
+      <c r="O74" s="3" t="inlineStr">
+        <is>
+          <t>9823413949</t>
+        </is>
+      </c>
+      <c r="P74" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q74" s="3" t="inlineStr"/>
+      <c r="R74" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 06:16:16 PM</t>
+        </is>
+      </c>
+      <c r="S74" s="3" t="inlineStr"/>
+      <c r="T74" s="3" t="inlineStr"/>
+      <c r="U74" s="3" t="inlineStr">
+        <is>
+          <t>9823413949</t>
+        </is>
+      </c>
+      <c r="V74" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 12:12:45 PM</t>
+        </is>
+      </c>
+      <c r="W74" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 06:16:16 PM</t>
+        </is>
+      </c>
+      <c r="X74" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y74" s="3" t="inlineStr">
+        <is>
+          <t>27.6594</t>
+        </is>
+      </c>
+      <c r="Z74" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA74" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB74" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC74" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD74" s="3" t="inlineStr"/>
+      <c r="AE74" s="3" t="inlineStr">
+        <is>
+          <t>Mahalxmi, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF74" s="3" t="inlineStr"/>
+      <c r="AG74" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH74" s="3" t="inlineStr"/>
+      <c r="AI74" s="3" t="inlineStr">
+        <is>
+          <t>06:04 hour</t>
+        </is>
+      </c>
+      <c r="AJ74" s="3" t="inlineStr"/>
+      <c r="AK74" s="3" t="inlineStr"/>
+      <c r="AL74" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM74" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN74" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO74" s="3" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="AP74" s="3" t="inlineStr">
+        <is>
+          <t>85.31701</t>
+        </is>
+      </c>
+      <c r="AQ74" s="3" t="inlineStr"/>
+      <c r="AR74" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS74" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT74" s="3" t="inlineStr">
+        <is>
+          <t>6h 3m</t>
+        </is>
+      </c>
+      <c r="AU74" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV74" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW74" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX74" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
@@ -1087,7 +1087,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -14887,10 +14887,8 @@
           <t>SY Panel  Nepal Ltd</t>
         </is>
       </c>
-      <c r="O73" s="3" t="inlineStr">
-        <is>
-          <t>9851338341</t>
-        </is>
+      <c r="O73" s="3" t="n">
+        <v>9851338341</v>
       </c>
       <c r="P73" s="3" t="inlineStr">
         <is>
@@ -14980,10 +14978,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN73" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN73" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO73" s="3" t="inlineStr">
         <is>
@@ -14994,7 +14990,7 @@
       <c r="AQ73" s="3" t="inlineStr"/>
       <c r="AR73" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS73" s="3" t="inlineStr">
@@ -15095,10 +15091,8 @@
           <t>Binda Adhikari</t>
         </is>
       </c>
-      <c r="O74" s="3" t="inlineStr">
-        <is>
-          <t>9823413949</t>
-        </is>
+      <c r="O74" s="3" t="n">
+        <v>9823413949</v>
       </c>
       <c r="P74" s="3" t="inlineStr">
         <is>
@@ -15133,10 +15127,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y74" s="3" t="inlineStr">
-        <is>
-          <t>27.6594</t>
-        </is>
+      <c r="Y74" s="3" t="n">
+        <v>27.6594</v>
       </c>
       <c r="Z74" s="3" t="inlineStr">
         <is>
@@ -15188,25 +15180,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN74" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN74" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO74" s="3" t="inlineStr">
         <is>
           <t>1,5</t>
         </is>
       </c>
-      <c r="AP74" s="3" t="inlineStr">
-        <is>
-          <t>85.31701</t>
-        </is>
+      <c r="AP74" s="3" t="n">
+        <v>85.31701</v>
       </c>
       <c r="AQ74" s="3" t="inlineStr"/>
       <c r="AR74" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS74" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>73.3%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>93.3%</t>
+          <t>94.1%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>22.7%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>1.3%</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>61.3%</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -893,20 +893,20 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Due to Configuration Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>0</v>
@@ -921,7 +921,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Due to Configuration Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -931,13 +931,13 @@
         <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>0</v>
@@ -949,11 +949,11 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Payment Inquiry</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0</v>
@@ -971,7 +971,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -1003,31 +1003,59 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Payment Inquiry</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C9" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D9" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E9" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="F8" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="G8" s="4" t="n">
+      <c r="F9" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="G9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="H8" s="4" t="n">
-        <v>56</v>
+      <c r="H9" s="4" t="n">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1041,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX74"/>
+  <dimension ref="A1:AX76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1087,7 +1115,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -15228,6 +15256,434 @@
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 6:40 PM</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr"/>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>Case : router damage   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>router damage</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353059</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>sumundra kyuju</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
+          <t>sumundra kyuju</t>
+        </is>
+      </c>
+      <c r="O75" s="3" t="inlineStr">
+        <is>
+          <t>9886277449</t>
+        </is>
+      </c>
+      <c r="P75" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q75" s="3" t="inlineStr"/>
+      <c r="R75" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 06:40:20 PM</t>
+        </is>
+      </c>
+      <c r="S75" s="3" t="inlineStr"/>
+      <c r="T75" s="3" t="inlineStr"/>
+      <c r="U75" s="3" t="inlineStr">
+        <is>
+          <t>9886277449</t>
+        </is>
+      </c>
+      <c r="V75" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 05:38:59 PM</t>
+        </is>
+      </c>
+      <c r="W75" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 06:40:20 PM</t>
+        </is>
+      </c>
+      <c r="X75" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y75" s="3" t="inlineStr">
+        <is>
+          <t>27.662759</t>
+        </is>
+      </c>
+      <c r="Z75" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA75" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB75" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC75" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD75" s="3" t="inlineStr"/>
+      <c r="AE75" s="3" t="inlineStr">
+        <is>
+          <t>Bhaktapur, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF75" s="3" t="inlineStr"/>
+      <c r="AG75" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH75" s="3" t="inlineStr"/>
+      <c r="AI75" s="3" t="inlineStr">
+        <is>
+          <t>01:02 hour</t>
+        </is>
+      </c>
+      <c r="AJ75" s="3" t="inlineStr"/>
+      <c r="AK75" s="3" t="inlineStr"/>
+      <c r="AL75" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM75" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN75" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO75" s="3" t="inlineStr">
+        <is>
+          <t>L11-3</t>
+        </is>
+      </c>
+      <c r="AP75" s="3" t="inlineStr">
+        <is>
+          <t>85.406755</t>
+        </is>
+      </c>
+      <c r="AQ75" s="3" t="inlineStr"/>
+      <c r="AR75" s="3" t="inlineStr">
+        <is>
+          <t>Case : router damage   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS75" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT75" s="3" t="inlineStr">
+        <is>
+          <t>1h 1m</t>
+        </is>
+      </c>
+      <c r="AU75" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV75" s="3" t="inlineStr">
+        <is>
+          <t>Case : router damage   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW75" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX75" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 6:38 PM</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr"/>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>Case : ROUTER CHANGE  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>ROUTER CHANGE</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351106</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Shrestha</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Shrestha</t>
+        </is>
+      </c>
+      <c r="O76" s="3" t="inlineStr">
+        <is>
+          <t>9863165880</t>
+        </is>
+      </c>
+      <c r="P76" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q76" s="3" t="inlineStr"/>
+      <c r="R76" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 06:38:33 PM</t>
+        </is>
+      </c>
+      <c r="S76" s="3" t="inlineStr"/>
+      <c r="T76" s="3" t="inlineStr"/>
+      <c r="U76" s="3" t="inlineStr">
+        <is>
+          <t>9863165880</t>
+        </is>
+      </c>
+      <c r="V76" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:24:33 AM</t>
+        </is>
+      </c>
+      <c r="W76" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 06:38:33 PM</t>
+        </is>
+      </c>
+      <c r="X76" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y76" s="3" t="inlineStr">
+        <is>
+          <t>27.649494</t>
+        </is>
+      </c>
+      <c r="Z76" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA76" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB76" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC76" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD76" s="3" t="inlineStr"/>
+      <c r="AE76" s="3" t="inlineStr">
+        <is>
+          <t>Millenium School, Imadole , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF76" s="3" t="inlineStr">
+        <is>
+          <t>ranishrestha14@yahoo.com</t>
+        </is>
+      </c>
+      <c r="AG76" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH76" s="3" t="inlineStr"/>
+      <c r="AI76" s="3" t="inlineStr">
+        <is>
+          <t>18:14 hour</t>
+        </is>
+      </c>
+      <c r="AJ76" s="3" t="inlineStr"/>
+      <c r="AK76" s="3" t="inlineStr"/>
+      <c r="AL76" s="3" t="inlineStr">
+        <is>
+          <t>Sanam Sadar</t>
+        </is>
+      </c>
+      <c r="AM76" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN76" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO76" s="3" t="inlineStr">
+        <is>
+          <t>L56-5</t>
+        </is>
+      </c>
+      <c r="AP76" s="3" t="inlineStr">
+        <is>
+          <t>85.346</t>
+        </is>
+      </c>
+      <c r="AQ76" s="3" t="inlineStr"/>
+      <c r="AR76" s="3" t="inlineStr">
+        <is>
+          <t>Case : ROUTER CHANGE  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS76" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT76" s="3" t="inlineStr">
+        <is>
+          <t>1d 8h 14m</t>
+        </is>
+      </c>
+      <c r="AU76" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV76" s="3" t="inlineStr">
+        <is>
+          <t>Case : ROUTER CHANGE  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW76" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX76" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
@@ -1115,7 +1115,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -15323,10 +15323,8 @@
           <t>sumundra kyuju</t>
         </is>
       </c>
-      <c r="O75" s="3" t="inlineStr">
-        <is>
-          <t>9886277449</t>
-        </is>
+      <c r="O75" s="3" t="n">
+        <v>9886277449</v>
       </c>
       <c r="P75" s="3" t="inlineStr">
         <is>
@@ -15361,10 +15359,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y75" s="3" t="inlineStr">
-        <is>
-          <t>27.662759</t>
-        </is>
+      <c r="Y75" s="3" t="n">
+        <v>27.662759</v>
       </c>
       <c r="Z75" s="3" t="inlineStr">
         <is>
@@ -15416,25 +15412,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN75" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN75" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO75" s="3" t="inlineStr">
         <is>
           <t>L11-3</t>
         </is>
       </c>
-      <c r="AP75" s="3" t="inlineStr">
-        <is>
-          <t>85.406755</t>
-        </is>
+      <c r="AP75" s="3" t="n">
+        <v>85.406755</v>
       </c>
       <c r="AQ75" s="3" t="inlineStr"/>
       <c r="AR75" s="3" t="inlineStr">
         <is>
-          <t>Case : router damage   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS75" s="3" t="inlineStr">
@@ -15535,10 +15527,8 @@
           <t>Nirajan Shrestha</t>
         </is>
       </c>
-      <c r="O76" s="3" t="inlineStr">
-        <is>
-          <t>9863165880</t>
-        </is>
+      <c r="O76" s="3" t="n">
+        <v>9863165880</v>
       </c>
       <c r="P76" s="3" t="inlineStr">
         <is>
@@ -15573,10 +15563,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y76" s="3" t="inlineStr">
-        <is>
-          <t>27.649494</t>
-        </is>
+      <c r="Y76" s="3" t="n">
+        <v>27.649494</v>
       </c>
       <c r="Z76" s="3" t="inlineStr">
         <is>
@@ -15632,25 +15620,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN76" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN76" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO76" s="3" t="inlineStr">
         <is>
           <t>L56-5</t>
         </is>
       </c>
-      <c r="AP76" s="3" t="inlineStr">
-        <is>
-          <t>85.346</t>
-        </is>
+      <c r="AP76" s="3" t="n">
+        <v>85.346</v>
       </c>
       <c r="AQ76" s="3" t="inlineStr"/>
       <c r="AR76" s="3" t="inlineStr">
         <is>
-          <t>Case : ROUTER CHANGE  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS76" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>73.7%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>16</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>94.1%</t>
+          <t>94.4%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>23.7%</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>60.5%</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -921,11 +921,11 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
@@ -934,10 +934,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>2</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>0</v>
@@ -949,11 +949,11 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0</v>
@@ -962,10 +962,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
@@ -1031,31 +1031,59 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade Dual Band</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B10" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C10" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D10" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E10" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="F10" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="G9" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>58</v>
+      <c r="G10" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1069,7 +1097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX76"/>
+  <dimension ref="A1:AX77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1115,7 +1143,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -15668,6 +15696,222 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 8:25 PM</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr"/>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>slow internet issue</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>TKT1347724</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>Saugat Kamal Upradi</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
+          <t>Saugat Kamal Upradi</t>
+        </is>
+      </c>
+      <c r="O77" s="3" t="inlineStr">
+        <is>
+          <t>9808035363</t>
+        </is>
+      </c>
+      <c r="P77" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q77" s="3" t="inlineStr"/>
+      <c r="R77" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 11:45:37 AM</t>
+        </is>
+      </c>
+      <c r="S77" s="3" t="inlineStr"/>
+      <c r="T77" s="3" t="inlineStr"/>
+      <c r="U77" s="3" t="inlineStr">
+        <is>
+          <t>KLK9808035363</t>
+        </is>
+      </c>
+      <c r="V77" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 08:58:11 PM</t>
+        </is>
+      </c>
+      <c r="W77" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 08:25:21 PM</t>
+        </is>
+      </c>
+      <c r="X77" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y77" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z77" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA77" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-CG Group</t>
+        </is>
+      </c>
+      <c r="AB77" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC77" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD77" s="3" t="inlineStr"/>
+      <c r="AE77" s="3" t="inlineStr">
+        <is>
+          <t>27.693722365366416, 85.2815403618628 GPS Coordinates Nearest: KAT004-01-3/7-ADB031 (114m Road) Map:</t>
+        </is>
+      </c>
+      <c r="AF77" s="3" t="inlineStr">
+        <is>
+          <t>9808035363@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG77" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade Dual Band</t>
+        </is>
+      </c>
+      <c r="AH77" s="3" t="inlineStr"/>
+      <c r="AI77" s="3" t="inlineStr">
+        <is>
+          <t>06:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ77" s="3" t="inlineStr"/>
+      <c r="AK77" s="3" t="inlineStr"/>
+      <c r="AL77" s="3" t="inlineStr">
+        <is>
+          <t>Anusha Adhikari</t>
+        </is>
+      </c>
+      <c r="AM77" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN77" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO77" s="3" t="inlineStr">
+        <is>
+          <t>1,3</t>
+        </is>
+      </c>
+      <c r="AP77" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ77" s="3" t="inlineStr"/>
+      <c r="AR77" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS77" s="3" t="inlineStr">
+        <is>
+          <t>8h 39m</t>
+        </is>
+      </c>
+      <c r="AT77" s="3" t="inlineStr">
+        <is>
+          <t>3d 23h 27m</t>
+        </is>
+      </c>
+      <c r="AU77" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV77" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW77" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX77" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>76.9%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>74.0%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>17</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>94.4%</t>
+          <t>94.7%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>24.7%</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>59.7%</t>
         </is>
       </c>
     </row>
@@ -1097,7 +1097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX77"/>
+  <dimension ref="A1:AX78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -15763,10 +15763,8 @@
           <t>Saugat Kamal Upradi</t>
         </is>
       </c>
-      <c r="O77" s="3" t="inlineStr">
-        <is>
-          <t>9808035363</t>
-        </is>
+      <c r="O77" s="3" t="n">
+        <v>9808035363</v>
       </c>
       <c r="P77" s="3" t="inlineStr">
         <is>
@@ -15801,10 +15799,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y77" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y77" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z77" s="3" t="inlineStr">
         <is>
@@ -15860,53 +15856,265 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN77" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN77" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO77" s="3" t="inlineStr">
         <is>
           <t>1,3</t>
         </is>
       </c>
-      <c r="AP77" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP77" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ77" s="3" t="inlineStr"/>
       <c r="AR77" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS77" s="3" t="inlineStr">
+        <is>
+          <t>8h 39m</t>
+        </is>
+      </c>
+      <c r="AT77" s="3" t="inlineStr">
+        <is>
+          <t>3d 23h 27m</t>
+        </is>
+      </c>
+      <c r="AU77" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV77" s="3" t="inlineStr">
+        <is>
           <t>Case : slow internet issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS77" s="3" t="inlineStr">
-        <is>
-          <t>8h 39m</t>
-        </is>
-      </c>
-      <c r="AT77" s="3" t="inlineStr">
-        <is>
-          <t>3d 23h 27m</t>
-        </is>
-      </c>
-      <c r="AU77" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV77" s="3" t="inlineStr">
+      <c r="AW77" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX77" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 8:30 PM</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr"/>
+      <c r="H78" s="3" t="inlineStr">
         <is>
           <t>Case : slow internet issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AW77" s="3" t="inlineStr">
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>slow internet issue</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>TKT1347724</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>Saugat Kamal Upradi</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
+          <t>Saugat Kamal Upradi</t>
+        </is>
+      </c>
+      <c r="O78" s="3" t="inlineStr">
+        <is>
+          <t>9808035363</t>
+        </is>
+      </c>
+      <c r="P78" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="AX77" s="3" t="inlineStr">
+      <c r="Q78" s="3" t="inlineStr"/>
+      <c r="R78" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 11:45:37 AM</t>
+        </is>
+      </c>
+      <c r="S78" s="3" t="inlineStr"/>
+      <c r="T78" s="3" t="inlineStr"/>
+      <c r="U78" s="3" t="inlineStr">
+        <is>
+          <t>KLK9808035363</t>
+        </is>
+      </c>
+      <c r="V78" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 08:58:11 PM</t>
+        </is>
+      </c>
+      <c r="W78" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 08:30:19 PM</t>
+        </is>
+      </c>
+      <c r="X78" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y78" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z78" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA78" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-CG Group</t>
+        </is>
+      </c>
+      <c r="AB78" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC78" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD78" s="3" t="inlineStr"/>
+      <c r="AE78" s="3" t="inlineStr">
+        <is>
+          <t>27.693722365366416, 85.2815403618628 GPS Coordinates Nearest: KAT004-01-3/7-ADB031 (114m Road) Map:</t>
+        </is>
+      </c>
+      <c r="AF78" s="3" t="inlineStr">
+        <is>
+          <t>9808035363@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG78" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade Dual Band</t>
+        </is>
+      </c>
+      <c r="AH78" s="3" t="inlineStr"/>
+      <c r="AI78" s="3" t="inlineStr">
+        <is>
+          <t>06:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ78" s="3" t="inlineStr"/>
+      <c r="AK78" s="3" t="inlineStr"/>
+      <c r="AL78" s="3" t="inlineStr">
+        <is>
+          <t>Anusha Adhikari</t>
+        </is>
+      </c>
+      <c r="AM78" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN78" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO78" s="3" t="inlineStr">
+        <is>
+          <t>1,3</t>
+        </is>
+      </c>
+      <c r="AP78" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ78" s="3" t="inlineStr"/>
+      <c r="AR78" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS78" s="3" t="inlineStr">
+        <is>
+          <t>8h 44m</t>
+        </is>
+      </c>
+      <c r="AT78" s="3" t="inlineStr">
+        <is>
+          <t>3d 23h 32m</t>
+        </is>
+      </c>
+      <c r="AU78" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV78" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW78" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX78" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
         </is>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Sep_2026.xlsx
@@ -1143,7 +1143,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -15971,10 +15971,8 @@
           <t>Saugat Kamal Upradi</t>
         </is>
       </c>
-      <c r="O78" s="3" t="inlineStr">
-        <is>
-          <t>9808035363</t>
-        </is>
+      <c r="O78" s="3" t="n">
+        <v>9808035363</v>
       </c>
       <c r="P78" s="3" t="inlineStr">
         <is>
@@ -16009,10 +16007,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y78" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y78" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z78" s="3" t="inlineStr">
         <is>
@@ -16068,25 +16064,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN78" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN78" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO78" s="3" t="inlineStr">
         <is>
           <t>1,3</t>
         </is>
       </c>
-      <c r="AP78" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP78" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ78" s="3" t="inlineStr"/>
       <c r="AR78" s="3" t="inlineStr">
         <is>
-          <t>Case : slow internet issue   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS78" s="3" t="inlineStr">
